--- a/Distribution_SAQ_20261003.xlsx
+++ b/Distribution_SAQ_20261003.xlsx
@@ -548,7 +548,7 @@
         </is>
       </c>
       <c r="C3" s="5" t="n">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
@@ -590,7 +590,7 @@
         </is>
       </c>
       <c r="C5" s="5" t="n">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
@@ -611,7 +611,7 @@
         </is>
       </c>
       <c r="C6" s="8" t="n">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
@@ -632,7 +632,7 @@
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
@@ -695,7 +695,7 @@
         </is>
       </c>
       <c r="C10" s="8" t="n">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
@@ -737,7 +737,7 @@
         </is>
       </c>
       <c r="C12" s="8" t="n">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         </is>
       </c>
       <c r="C14" s="8" t="n">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
@@ -821,7 +821,7 @@
         </is>
       </c>
       <c r="C16" s="8" t="n">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
@@ -842,7 +842,7 @@
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
@@ -863,7 +863,7 @@
         </is>
       </c>
       <c r="C18" s="8" t="n">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D18" s="7" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         </is>
       </c>
       <c r="C20" s="8" t="n">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="D20" s="7" t="inlineStr">
         <is>
@@ -926,7 +926,7 @@
         </is>
       </c>
       <c r="C21" s="5" t="n">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
@@ -968,7 +968,7 @@
         </is>
       </c>
       <c r="C23" s="5" t="n">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
@@ -1010,7 +1010,7 @@
         </is>
       </c>
       <c r="C25" s="5" t="n">
-        <v>179</v>
+        <v>171</v>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         </is>
       </c>
       <c r="C26" s="8" t="n">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="D26" s="7" t="inlineStr">
         <is>
@@ -1052,7 +1052,7 @@
         </is>
       </c>
       <c r="C27" s="5" t="n">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
@@ -1073,7 +1073,7 @@
         </is>
       </c>
       <c r="C28" s="8" t="n">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="D28" s="7" t="inlineStr">
         <is>
@@ -1094,7 +1094,7 @@
         </is>
       </c>
       <c r="C29" s="5" t="n">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
@@ -1115,7 +1115,7 @@
         </is>
       </c>
       <c r="C30" s="8" t="n">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D30" s="7" t="inlineStr">
         <is>
@@ -1199,7 +1199,7 @@
         </is>
       </c>
       <c r="C34" s="8" t="n">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="D34" s="7" t="inlineStr">
         <is>
@@ -1220,7 +1220,7 @@
         </is>
       </c>
       <c r="C35" s="5" t="n">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
@@ -1262,7 +1262,7 @@
         </is>
       </c>
       <c r="C37" s="5" t="n">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
@@ -1283,7 +1283,7 @@
         </is>
       </c>
       <c r="C38" s="8" t="n">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="D38" s="7" t="inlineStr">
         <is>
@@ -1325,7 +1325,7 @@
         </is>
       </c>
       <c r="C40" s="8" t="n">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="D40" s="7" t="inlineStr">
         <is>
@@ -1346,7 +1346,7 @@
         </is>
       </c>
       <c r="C41" s="5" t="n">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
@@ -1388,7 +1388,7 @@
         </is>
       </c>
       <c r="C43" s="5" t="n">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
@@ -1409,7 +1409,7 @@
         </is>
       </c>
       <c r="C44" s="8" t="n">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="D44" s="7" t="inlineStr">
         <is>
@@ -1430,7 +1430,7 @@
         </is>
       </c>
       <c r="C45" s="5" t="n">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
@@ -1514,7 +1514,7 @@
         </is>
       </c>
       <c r="C49" s="5" t="n">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
@@ -1535,7 +1535,7 @@
         </is>
       </c>
       <c r="C50" s="8" t="n">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="D50" s="7" t="inlineStr">
         <is>
@@ -1598,7 +1598,7 @@
         </is>
       </c>
       <c r="C53" s="5" t="n">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
@@ -1640,7 +1640,7 @@
         </is>
       </c>
       <c r="C55" s="5" t="n">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
@@ -1661,7 +1661,7 @@
         </is>
       </c>
       <c r="C56" s="8" t="n">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="D56" s="7" t="inlineStr">
         <is>
@@ -1682,7 +1682,7 @@
         </is>
       </c>
       <c r="C57" s="3" t="n">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
@@ -1724,7 +1724,7 @@
         </is>
       </c>
       <c r="C59" s="5" t="n">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         </is>
       </c>
       <c r="C60" s="8" t="n">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="D60" s="7" t="inlineStr">
         <is>
@@ -1787,7 +1787,7 @@
         </is>
       </c>
       <c r="C62" s="8" t="n">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D62" s="7" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
         </is>
       </c>
       <c r="C63" s="5" t="n">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
@@ -1829,7 +1829,7 @@
         </is>
       </c>
       <c r="C64" s="8" t="n">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D64" s="7" t="inlineStr">
         <is>
@@ -1934,7 +1934,7 @@
         </is>
       </c>
       <c r="C69" s="5" t="n">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
@@ -1955,7 +1955,7 @@
         </is>
       </c>
       <c r="C70" s="8" t="n">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D70" s="7" t="inlineStr">
         <is>
@@ -1976,7 +1976,7 @@
         </is>
       </c>
       <c r="C71" s="5" t="n">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D71" s="4" t="inlineStr">
         <is>
@@ -2018,7 +2018,7 @@
         </is>
       </c>
       <c r="C73" s="5" t="n">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="D73" s="4" t="inlineStr">
         <is>
@@ -2039,7 +2039,7 @@
         </is>
       </c>
       <c r="C74" s="8" t="n">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="D74" s="7" t="inlineStr">
         <is>
@@ -2060,7 +2060,7 @@
         </is>
       </c>
       <c r="C75" s="5" t="n">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D75" s="4" t="inlineStr">
         <is>
@@ -2102,7 +2102,7 @@
         </is>
       </c>
       <c r="C77" s="5" t="n">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="D77" s="4" t="inlineStr">
         <is>
@@ -2165,7 +2165,7 @@
         </is>
       </c>
       <c r="C80" s="8" t="n">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D80" s="7" t="inlineStr">
         <is>
@@ -2207,7 +2207,7 @@
         </is>
       </c>
       <c r="C82" s="8" t="n">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D82" s="7" t="inlineStr">
         <is>
@@ -2228,7 +2228,7 @@
         </is>
       </c>
       <c r="C83" s="5" t="n">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="D83" s="4" t="inlineStr">
         <is>
@@ -2270,7 +2270,7 @@
         </is>
       </c>
       <c r="C85" s="5" t="n">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D85" s="4" t="inlineStr">
         <is>
@@ -2291,7 +2291,7 @@
         </is>
       </c>
       <c r="C86" s="8" t="n">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="D86" s="7" t="inlineStr">
         <is>
@@ -2312,7 +2312,7 @@
         </is>
       </c>
       <c r="C87" s="5" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D87" s="4" t="inlineStr">
         <is>
@@ -2396,7 +2396,7 @@
         </is>
       </c>
       <c r="C91" s="5" t="n">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D91" s="4" t="inlineStr">
         <is>
@@ -2417,7 +2417,7 @@
         </is>
       </c>
       <c r="C92" s="8" t="n">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="D92" s="7" t="inlineStr">
         <is>
@@ -2459,7 +2459,7 @@
         </is>
       </c>
       <c r="C94" s="6" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D94" s="7" t="inlineStr">
         <is>
@@ -2501,7 +2501,7 @@
         </is>
       </c>
       <c r="C96" s="8" t="n">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D96" s="7" t="inlineStr">
         <is>
@@ -2522,7 +2522,7 @@
         </is>
       </c>
       <c r="C97" s="5" t="n">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D97" s="4" t="inlineStr">
         <is>
@@ -2543,7 +2543,7 @@
         </is>
       </c>
       <c r="C98" s="8" t="n">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="D98" s="7" t="inlineStr">
         <is>
@@ -2564,7 +2564,7 @@
         </is>
       </c>
       <c r="C99" s="5" t="n">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="D99" s="4" t="inlineStr">
         <is>
@@ -2585,7 +2585,7 @@
         </is>
       </c>
       <c r="C100" s="8" t="n">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="D100" s="7" t="inlineStr">
         <is>
@@ -2606,7 +2606,7 @@
         </is>
       </c>
       <c r="C101" s="5" t="n">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D101" s="4" t="inlineStr">
         <is>
@@ -2648,7 +2648,7 @@
         </is>
       </c>
       <c r="C103" s="5" t="n">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D103" s="4" t="inlineStr">
         <is>
@@ -2669,7 +2669,7 @@
         </is>
       </c>
       <c r="C104" s="8" t="n">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D104" s="7" t="inlineStr">
         <is>
@@ -2690,7 +2690,7 @@
         </is>
       </c>
       <c r="C105" s="3" t="n">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="D105" s="4" t="inlineStr">
         <is>
@@ -2711,7 +2711,7 @@
         </is>
       </c>
       <c r="C106" s="8" t="n">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D106" s="7" t="inlineStr">
         <is>
@@ -2732,7 +2732,7 @@
         </is>
       </c>
       <c r="C107" s="3" t="n">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D107" s="4" t="inlineStr">
         <is>
@@ -2753,7 +2753,7 @@
         </is>
       </c>
       <c r="C108" s="8" t="n">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D108" s="7" t="inlineStr">
         <is>
@@ -2816,7 +2816,7 @@
         </is>
       </c>
       <c r="C111" s="5" t="n">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D111" s="4" t="inlineStr">
         <is>
@@ -2921,7 +2921,7 @@
         </is>
       </c>
       <c r="C116" s="8" t="n">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D116" s="7" t="inlineStr">
         <is>
@@ -2942,7 +2942,7 @@
         </is>
       </c>
       <c r="C117" s="5" t="n">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D117" s="4" t="inlineStr">
         <is>
@@ -2984,7 +2984,7 @@
         </is>
       </c>
       <c r="C119" s="5" t="n">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="D119" s="4" t="inlineStr">
         <is>
@@ -3026,7 +3026,7 @@
         </is>
       </c>
       <c r="C121" s="3" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D121" s="4" t="inlineStr">
         <is>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="C122" s="8" t="n">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="D122" s="7" t="inlineStr">
         <is>
@@ -3068,7 +3068,7 @@
         </is>
       </c>
       <c r="C123" s="5" t="n">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D123" s="4" t="inlineStr">
         <is>
@@ -3110,7 +3110,7 @@
         </is>
       </c>
       <c r="C125" s="5" t="n">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="D125" s="4" t="inlineStr">
         <is>
@@ -3131,7 +3131,7 @@
         </is>
       </c>
       <c r="C126" s="8" t="n">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D126" s="7" t="inlineStr">
         <is>
@@ -3152,7 +3152,7 @@
         </is>
       </c>
       <c r="C127" s="5" t="n">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D127" s="4" t="inlineStr">
         <is>
@@ -3173,7 +3173,7 @@
         </is>
       </c>
       <c r="C128" s="8" t="n">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="D128" s="7" t="inlineStr">
         <is>
@@ -3194,7 +3194,7 @@
         </is>
       </c>
       <c r="C129" s="5" t="n">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="D129" s="4" t="inlineStr">
         <is>
@@ -3278,7 +3278,7 @@
         </is>
       </c>
       <c r="C133" s="5" t="n">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D133" s="4" t="inlineStr">
         <is>
@@ -3299,7 +3299,7 @@
         </is>
       </c>
       <c r="C134" s="8" t="n">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="D134" s="7" t="inlineStr">
         <is>
@@ -3320,7 +3320,7 @@
         </is>
       </c>
       <c r="C135" s="5" t="n">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D135" s="4" t="inlineStr">
         <is>
@@ -3467,7 +3467,7 @@
         </is>
       </c>
       <c r="C142" s="6" t="n">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="D142" s="7" t="inlineStr">
         <is>
@@ -3488,7 +3488,7 @@
         </is>
       </c>
       <c r="C143" s="5" t="n">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D143" s="4" t="inlineStr">
         <is>
@@ -3509,7 +3509,7 @@
         </is>
       </c>
       <c r="C144" s="8" t="n">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D144" s="7" t="inlineStr">
         <is>
@@ -3551,7 +3551,7 @@
         </is>
       </c>
       <c r="C146" s="8" t="n">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="D146" s="7" t="inlineStr">
         <is>
@@ -3593,7 +3593,7 @@
         </is>
       </c>
       <c r="C148" s="8" t="n">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="D148" s="7" t="inlineStr">
         <is>
@@ -3614,7 +3614,7 @@
         </is>
       </c>
       <c r="C149" s="5" t="n">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="D149" s="4" t="inlineStr">
         <is>
@@ -3635,7 +3635,7 @@
         </is>
       </c>
       <c r="C150" s="6" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D150" s="7" t="inlineStr">
         <is>
@@ -3677,7 +3677,7 @@
         </is>
       </c>
       <c r="C152" s="8" t="n">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D152" s="7" t="inlineStr">
         <is>
@@ -3719,7 +3719,7 @@
         </is>
       </c>
       <c r="C154" s="6" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D154" s="7" t="inlineStr">
         <is>
@@ -3866,7 +3866,7 @@
         </is>
       </c>
       <c r="C161" s="3" t="n">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D161" s="4" t="inlineStr">
         <is>
@@ -3929,7 +3929,7 @@
         </is>
       </c>
       <c r="C164" s="8" t="n">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="D164" s="7" t="inlineStr">
         <is>
@@ -4118,7 +4118,7 @@
         </is>
       </c>
       <c r="C173" s="3" t="n">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D173" s="4" t="inlineStr">
         <is>
@@ -4181,7 +4181,7 @@
         </is>
       </c>
       <c r="C176" s="6" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D176" s="7" t="inlineStr">
         <is>
@@ -4265,7 +4265,7 @@
         </is>
       </c>
       <c r="C180" s="8" t="n">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D180" s="7" t="inlineStr">
         <is>
@@ -4391,7 +4391,7 @@
         </is>
       </c>
       <c r="C186" s="8" t="n">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D186" s="7" t="inlineStr">
         <is>
@@ -4895,7 +4895,7 @@
         </is>
       </c>
       <c r="C210" s="6" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D210" s="7" t="inlineStr">
         <is>
@@ -5361,7 +5361,7 @@
         </is>
       </c>
       <c r="C232" s="6" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D232" s="7" t="inlineStr">
         <is>
@@ -5826,8 +5826,8 @@
           <t>Palm Bay Framboise Bleue Citron Zero Sucre (4 x 355 ml)</t>
         </is>
       </c>
-      <c r="C254" s="6" t="n">
-        <v>1</v>
+      <c r="C254" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="D254" s="7" t="inlineStr">
         <is>
@@ -5997,7 +5997,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2107"/>
+  <dimension ref="A1:F2105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -6097,7 +6097,7 @@
         </is>
       </c>
       <c r="F3" s="11" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="4">
@@ -6127,7 +6127,7 @@
         </is>
       </c>
       <c r="F4" s="11" t="n">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="5">
@@ -6217,7 +6217,7 @@
         </is>
       </c>
       <c r="F7" s="11" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="8">
@@ -6307,7 +6307,7 @@
         </is>
       </c>
       <c r="F10" s="11" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="11">
@@ -6337,7 +6337,7 @@
         </is>
       </c>
       <c r="F11" s="11" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="12">
@@ -6607,7 +6607,7 @@
         </is>
       </c>
       <c r="F20" s="11" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="21">
@@ -6637,7 +6637,7 @@
         </is>
       </c>
       <c r="F21" s="11" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="22">
@@ -6967,7 +6967,7 @@
         </is>
       </c>
       <c r="F32" s="11" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="33">
@@ -7207,7 +7207,7 @@
         </is>
       </c>
       <c r="F40" s="11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="41">
@@ -7297,7 +7297,7 @@
         </is>
       </c>
       <c r="F43" s="11" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="44">
@@ -7327,7 +7327,7 @@
         </is>
       </c>
       <c r="F44" s="11" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="45">
@@ -7447,7 +7447,7 @@
         </is>
       </c>
       <c r="F48" s="11" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="49">
@@ -7537,7 +7537,7 @@
         </is>
       </c>
       <c r="F51" s="11" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="52">
@@ -7627,7 +7627,7 @@
         </is>
       </c>
       <c r="F54" s="11" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="55">
@@ -7927,7 +7927,7 @@
         </is>
       </c>
       <c r="F64" s="11" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="65">
@@ -7957,7 +7957,7 @@
         </is>
       </c>
       <c r="F65" s="11" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="66">
@@ -8047,7 +8047,7 @@
         </is>
       </c>
       <c r="F68" s="11" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="69">
@@ -8077,7 +8077,7 @@
         </is>
       </c>
       <c r="F69" s="11" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="70">
@@ -8107,7 +8107,7 @@
         </is>
       </c>
       <c r="F70" s="11" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
     <row r="71">
@@ -8167,7 +8167,7 @@
         </is>
       </c>
       <c r="F72" s="11" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="73">
@@ -8197,7 +8197,7 @@
         </is>
       </c>
       <c r="F73" s="11" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
     </row>
     <row r="74">
@@ -8227,7 +8227,7 @@
         </is>
       </c>
       <c r="F74" s="11" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="75">
@@ -8437,7 +8437,7 @@
         </is>
       </c>
       <c r="F81" s="11" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="82">
@@ -8677,7 +8677,7 @@
         </is>
       </c>
       <c r="F89" s="11" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="90">
@@ -8947,7 +8947,7 @@
         </is>
       </c>
       <c r="F98" s="11" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="99">
@@ -8977,7 +8977,7 @@
         </is>
       </c>
       <c r="F99" s="11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="100">
@@ -9037,7 +9037,7 @@
         </is>
       </c>
       <c r="F101" s="11" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="102">
@@ -9127,7 +9127,7 @@
         </is>
       </c>
       <c r="F104" s="11" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="105">
@@ -9367,7 +9367,7 @@
         </is>
       </c>
       <c r="F112" s="11" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="113">
@@ -9397,7 +9397,7 @@
         </is>
       </c>
       <c r="F113" s="11" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="114">
@@ -9427,7 +9427,7 @@
         </is>
       </c>
       <c r="F114" s="11" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
     <row r="115">
@@ -9577,7 +9577,7 @@
         </is>
       </c>
       <c r="F119" s="11" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="120">
@@ -9607,7 +9607,7 @@
         </is>
       </c>
       <c r="F120" s="11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="121">
@@ -9667,7 +9667,7 @@
         </is>
       </c>
       <c r="F122" s="11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="123">
@@ -9787,7 +9787,7 @@
         </is>
       </c>
       <c r="F126" s="11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="127">
@@ -10027,7 +10027,7 @@
         </is>
       </c>
       <c r="F134" s="11" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="135">
@@ -10327,7 +10327,7 @@
         </is>
       </c>
       <c r="F144" s="11" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="145">
@@ -10567,7 +10567,7 @@
         </is>
       </c>
       <c r="F152" s="11" t="n">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="153">
@@ -10657,7 +10657,7 @@
         </is>
       </c>
       <c r="F155" s="11" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="156">
@@ -10777,7 +10777,7 @@
         </is>
       </c>
       <c r="F159" s="11" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="160">
@@ -10927,7 +10927,7 @@
         </is>
       </c>
       <c r="F164" s="11" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="165">
@@ -11047,7 +11047,7 @@
         </is>
       </c>
       <c r="F168" s="11" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="169">
@@ -11107,7 +11107,7 @@
         </is>
       </c>
       <c r="F170" s="11" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="171">
@@ -11167,7 +11167,7 @@
         </is>
       </c>
       <c r="F172" s="11" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="173">
@@ -11183,12 +11183,12 @@
       </c>
       <c r="C173" s="11" t="inlineStr">
         <is>
-          <t>Place Dupuis</t>
+          <t>De Maisonneuve - City Councillors</t>
         </is>
       </c>
       <c r="D173" s="11" t="inlineStr">
         <is>
-          <t>SAQ Express</t>
+          <t>SAQ Sélection</t>
         </is>
       </c>
       <c r="E173" s="11" t="inlineStr">
@@ -11197,7 +11197,7 @@
         </is>
       </c>
       <c r="F173" s="11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="174">
@@ -11213,12 +11213,12 @@
       </c>
       <c r="C174" s="11" t="inlineStr">
         <is>
-          <t>De Maisonneuve - City Councillors</t>
+          <t>Halles de la Gare</t>
         </is>
       </c>
       <c r="D174" s="11" t="inlineStr">
         <is>
-          <t>SAQ Sélection</t>
+          <t>SAQ</t>
         </is>
       </c>
       <c r="E174" s="11" t="inlineStr">
@@ -11227,7 +11227,7 @@
         </is>
       </c>
       <c r="F174" s="11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="175">
@@ -11243,7 +11243,7 @@
       </c>
       <c r="C175" s="11" t="inlineStr">
         <is>
-          <t>Halles de la Gare</t>
+          <t>Centre Eaton</t>
         </is>
       </c>
       <c r="D175" s="11" t="inlineStr">
@@ -11257,7 +11257,7 @@
         </is>
       </c>
       <c r="F175" s="11" t="n">
-        <v>3</v>
+        <v>40</v>
       </c>
     </row>
     <row r="176">
@@ -11273,7 +11273,7 @@
       </c>
       <c r="C176" s="11" t="inlineStr">
         <is>
-          <t>Centre Eaton</t>
+          <t>La Cité - Les Galeries du Parc</t>
         </is>
       </c>
       <c r="D176" s="11" t="inlineStr">
@@ -11287,7 +11287,7 @@
         </is>
       </c>
       <c r="F176" s="11" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
     </row>
     <row r="177">
@@ -11303,7 +11303,7 @@
       </c>
       <c r="C177" s="11" t="inlineStr">
         <is>
-          <t>La Cité - Les Galeries du Parc</t>
+          <t>Griffintown</t>
         </is>
       </c>
       <c r="D177" s="11" t="inlineStr">
@@ -11317,7 +11317,7 @@
         </is>
       </c>
       <c r="F177" s="11" t="n">
-        <v>45</v>
+        <v>24</v>
       </c>
     </row>
     <row r="178">
@@ -11333,7 +11333,7 @@
       </c>
       <c r="C178" s="11" t="inlineStr">
         <is>
-          <t>Griffintown</t>
+          <t>St-Laurent - Des Pins</t>
         </is>
       </c>
       <c r="D178" s="11" t="inlineStr">
@@ -11347,7 +11347,7 @@
         </is>
       </c>
       <c r="F178" s="11" t="n">
-        <v>24</v>
+        <v>78</v>
       </c>
     </row>
     <row r="179">
@@ -11363,7 +11363,7 @@
       </c>
       <c r="C179" s="11" t="inlineStr">
         <is>
-          <t>St-Laurent - Des Pins</t>
+          <t>Ste-Catherine est/ De Lorimier</t>
         </is>
       </c>
       <c r="D179" s="11" t="inlineStr">
@@ -11377,7 +11377,7 @@
         </is>
       </c>
       <c r="F179" s="11" t="n">
-        <v>78</v>
+        <v>5</v>
       </c>
     </row>
     <row r="180">
@@ -11393,12 +11393,12 @@
       </c>
       <c r="C180" s="11" t="inlineStr">
         <is>
-          <t>Ste-Catherine est/ De Lorimier</t>
+          <t>Ste-Catherine Ouest - Stanley</t>
         </is>
       </c>
       <c r="D180" s="11" t="inlineStr">
         <is>
-          <t>SAQ</t>
+          <t>SAQ Express</t>
         </is>
       </c>
       <c r="E180" s="11" t="inlineStr">
@@ -11407,7 +11407,7 @@
         </is>
       </c>
       <c r="F180" s="11" t="n">
-        <v>6</v>
+        <v>29</v>
       </c>
     </row>
     <row r="181">
@@ -11423,12 +11423,12 @@
       </c>
       <c r="C181" s="11" t="inlineStr">
         <is>
-          <t>Ste-Catherine Ouest - Stanley</t>
+          <t>De la Montagne</t>
         </is>
       </c>
       <c r="D181" s="11" t="inlineStr">
         <is>
-          <t>SAQ Express</t>
+          <t>SAQ Sélection</t>
         </is>
       </c>
       <c r="E181" s="11" t="inlineStr">
@@ -11437,7 +11437,7 @@
         </is>
       </c>
       <c r="F181" s="11" t="n">
-        <v>34</v>
+        <v>3</v>
       </c>
     </row>
     <row r="182">
@@ -11467,7 +11467,7 @@
         </is>
       </c>
       <c r="F182" s="11" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="183">
@@ -11527,7 +11527,7 @@
         </is>
       </c>
       <c r="F184" s="11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="185">
@@ -11677,7 +11677,7 @@
         </is>
       </c>
       <c r="F189" s="11" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="190">
@@ -11857,7 +11857,7 @@
         </is>
       </c>
       <c r="F195" s="11" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="196">
@@ -11977,7 +11977,7 @@
         </is>
       </c>
       <c r="F199" s="11" t="n">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="200">
@@ -12007,7 +12007,7 @@
         </is>
       </c>
       <c r="F200" s="11" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
     </row>
     <row r="201">
@@ -12037,7 +12037,7 @@
         </is>
       </c>
       <c r="F201" s="11" t="n">
-        <v>78</v>
+        <v>73</v>
       </c>
     </row>
     <row r="202">
@@ -12127,7 +12127,7 @@
         </is>
       </c>
       <c r="F204" s="11" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="205">
@@ -12157,7 +12157,7 @@
         </is>
       </c>
       <c r="F205" s="11" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="206">
@@ -12217,7 +12217,7 @@
         </is>
       </c>
       <c r="F207" s="11" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="208">
@@ -12353,12 +12353,12 @@
       </c>
       <c r="C212" s="11" t="inlineStr">
         <is>
-          <t>Place Dupuis</t>
+          <t>Halles de la Gare</t>
         </is>
       </c>
       <c r="D212" s="11" t="inlineStr">
         <is>
-          <t>SAQ Express</t>
+          <t>SAQ</t>
         </is>
       </c>
       <c r="E212" s="11" t="inlineStr">
@@ -12367,7 +12367,7 @@
         </is>
       </c>
       <c r="F212" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="213">
@@ -12383,7 +12383,7 @@
       </c>
       <c r="C213" s="11" t="inlineStr">
         <is>
-          <t>Halles de la Gare</t>
+          <t>La Cité - Les Galeries du Parc</t>
         </is>
       </c>
       <c r="D213" s="11" t="inlineStr">
@@ -12397,7 +12397,7 @@
         </is>
       </c>
       <c r="F213" s="11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="214">
@@ -12413,7 +12413,7 @@
       </c>
       <c r="C214" s="11" t="inlineStr">
         <is>
-          <t>La Cité - Les Galeries du Parc</t>
+          <t>Ste-Catherine est/ De Lorimier</t>
         </is>
       </c>
       <c r="D214" s="11" t="inlineStr">
@@ -12443,12 +12443,12 @@
       </c>
       <c r="C215" s="11" t="inlineStr">
         <is>
-          <t>Ste-Catherine est/ De Lorimier</t>
+          <t>Ste-Catherine Ouest - Stanley</t>
         </is>
       </c>
       <c r="D215" s="11" t="inlineStr">
         <is>
-          <t>SAQ</t>
+          <t>SAQ Express</t>
         </is>
       </c>
       <c r="E215" s="11" t="inlineStr">
@@ -12457,7 +12457,7 @@
         </is>
       </c>
       <c r="F215" s="11" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="216">
@@ -12473,12 +12473,12 @@
       </c>
       <c r="C216" s="11" t="inlineStr">
         <is>
-          <t>Ste-Catherine Ouest - Stanley</t>
+          <t>Saint-Denis - Rachel</t>
         </is>
       </c>
       <c r="D216" s="11" t="inlineStr">
         <is>
-          <t>SAQ Express</t>
+          <t>SAQ</t>
         </is>
       </c>
       <c r="E216" s="11" t="inlineStr">
@@ -12487,7 +12487,7 @@
         </is>
       </c>
       <c r="F216" s="11" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
     </row>
     <row r="217">
@@ -12503,7 +12503,7 @@
       </c>
       <c r="C217" s="11" t="inlineStr">
         <is>
-          <t>Saint-Denis - Rachel</t>
+          <t>Faubourg Sainte-Catherine</t>
         </is>
       </c>
       <c r="D217" s="11" t="inlineStr">
@@ -12517,7 +12517,7 @@
         </is>
       </c>
       <c r="F217" s="11" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="218">
@@ -12533,12 +12533,12 @@
       </c>
       <c r="C218" s="11" t="inlineStr">
         <is>
-          <t>Faubourg Sainte-Catherine</t>
+          <t>Mont-Royal Est - Mentana</t>
         </is>
       </c>
       <c r="D218" s="11" t="inlineStr">
         <is>
-          <t>SAQ</t>
+          <t>SAQ Express</t>
         </is>
       </c>
       <c r="E218" s="11" t="inlineStr">
@@ -12547,7 +12547,7 @@
         </is>
       </c>
       <c r="F218" s="11" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="219">
@@ -12563,12 +12563,12 @@
       </c>
       <c r="C219" s="11" t="inlineStr">
         <is>
-          <t>Mont-Royal Est - Mentana</t>
+          <t>Sainte-Catherine Ouest - Lambert Closse</t>
         </is>
       </c>
       <c r="D219" s="11" t="inlineStr">
         <is>
-          <t>SAQ Express</t>
+          <t>SAQ</t>
         </is>
       </c>
       <c r="E219" s="11" t="inlineStr">
@@ -12577,7 +12577,7 @@
         </is>
       </c>
       <c r="F219" s="11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="220">
@@ -12593,7 +12593,7 @@
       </c>
       <c r="C220" s="11" t="inlineStr">
         <is>
-          <t>Sainte-Catherine Ouest - Lambert Closse</t>
+          <t>Saint-Lambert - Centre-ville</t>
         </is>
       </c>
       <c r="D220" s="11" t="inlineStr">
@@ -12603,11 +12603,11 @@
       </c>
       <c r="E220" s="11" t="inlineStr">
         <is>
-          <t>Montréal</t>
+          <t>Saint-Lambert</t>
         </is>
       </c>
       <c r="F220" s="11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="221">
@@ -12623,21 +12623,21 @@
       </c>
       <c r="C221" s="11" t="inlineStr">
         <is>
-          <t>Saint-Lambert - Centre-ville</t>
+          <t>Marché Atwater</t>
         </is>
       </c>
       <c r="D221" s="11" t="inlineStr">
         <is>
-          <t>SAQ</t>
+          <t>SAQ Sélection</t>
         </is>
       </c>
       <c r="E221" s="11" t="inlineStr">
         <is>
-          <t>Saint-Lambert</t>
+          <t>Montréal</t>
         </is>
       </c>
       <c r="F221" s="11" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="222">
@@ -12937,7 +12937,7 @@
         </is>
       </c>
       <c r="F231" s="11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="232">
@@ -12967,7 +12967,7 @@
         </is>
       </c>
       <c r="F232" s="11" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="233">
@@ -13027,7 +13027,7 @@
         </is>
       </c>
       <c r="F234" s="11" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="235">
@@ -13057,7 +13057,7 @@
         </is>
       </c>
       <c r="F235" s="11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="236">
@@ -13597,7 +13597,7 @@
         </is>
       </c>
       <c r="F253" s="11" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="254">
@@ -13627,7 +13627,7 @@
         </is>
       </c>
       <c r="F254" s="11" t="n">
-        <v>31</v>
+        <v>27</v>
       </c>
     </row>
     <row r="255">
@@ -13747,7 +13747,7 @@
         </is>
       </c>
       <c r="F258" s="11" t="n">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="259">
@@ -13867,7 +13867,7 @@
         </is>
       </c>
       <c r="F262" s="11" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="263">
@@ -13927,7 +13927,7 @@
         </is>
       </c>
       <c r="F264" s="11" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="265">
@@ -14377,7 +14377,7 @@
         </is>
       </c>
       <c r="F279" s="11" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="280">
@@ -14437,7 +14437,7 @@
         </is>
       </c>
       <c r="F281" s="11" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="282">
@@ -15667,7 +15667,7 @@
         </is>
       </c>
       <c r="F322" s="11" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="323">
@@ -15967,7 +15967,7 @@
         </is>
       </c>
       <c r="F332" s="11" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="333">
@@ -16027,7 +16027,7 @@
         </is>
       </c>
       <c r="F334" s="11" t="n">
-        <v>35</v>
+        <v>32</v>
       </c>
     </row>
     <row r="335">
@@ -16267,7 +16267,7 @@
         </is>
       </c>
       <c r="F342" s="11" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="343">
@@ -16357,7 +16357,7 @@
         </is>
       </c>
       <c r="F345" s="11" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
     </row>
     <row r="346">
@@ -16537,7 +16537,7 @@
         </is>
       </c>
       <c r="F351" s="11" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="352">
@@ -17137,7 +17137,7 @@
         </is>
       </c>
       <c r="F371" s="11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="372">
@@ -17167,7 +17167,7 @@
         </is>
       </c>
       <c r="F372" s="11" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="373">
@@ -17317,7 +17317,7 @@
         </is>
       </c>
       <c r="F377" s="11" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="378">
@@ -17377,7 +17377,7 @@
         </is>
       </c>
       <c r="F379" s="11" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="380">
@@ -17587,7 +17587,7 @@
         </is>
       </c>
       <c r="F386" s="11" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="387">
@@ -18097,7 +18097,7 @@
         </is>
       </c>
       <c r="F403" s="11" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="404">
@@ -18307,7 +18307,7 @@
         </is>
       </c>
       <c r="F410" s="11" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="411">
@@ -18383,12 +18383,12 @@
       </c>
       <c r="C413" s="11" t="inlineStr">
         <is>
-          <t>De Maisonneuve - City Councillors</t>
+          <t>Halles de la Gare</t>
         </is>
       </c>
       <c r="D413" s="11" t="inlineStr">
         <is>
-          <t>SAQ Sélection</t>
+          <t>SAQ</t>
         </is>
       </c>
       <c r="E413" s="11" t="inlineStr">
@@ -18413,7 +18413,7 @@
       </c>
       <c r="C414" s="11" t="inlineStr">
         <is>
-          <t>Halles de la Gare</t>
+          <t>La Cité - Les Galeries du Parc</t>
         </is>
       </c>
       <c r="D414" s="11" t="inlineStr">
@@ -18427,7 +18427,7 @@
         </is>
       </c>
       <c r="F414" s="11" t="n">
-        <v>1</v>
+        <v>28</v>
       </c>
     </row>
     <row r="415">
@@ -18443,7 +18443,7 @@
       </c>
       <c r="C415" s="11" t="inlineStr">
         <is>
-          <t>La Cité - Les Galeries du Parc</t>
+          <t>Griffintown</t>
         </is>
       </c>
       <c r="D415" s="11" t="inlineStr">
@@ -18457,7 +18457,7 @@
         </is>
       </c>
       <c r="F415" s="11" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
     </row>
     <row r="416">
@@ -18473,7 +18473,7 @@
       </c>
       <c r="C416" s="11" t="inlineStr">
         <is>
-          <t>Griffintown</t>
+          <t>St-Laurent - Des Pins</t>
         </is>
       </c>
       <c r="D416" s="11" t="inlineStr">
@@ -18487,7 +18487,7 @@
         </is>
       </c>
       <c r="F416" s="11" t="n">
-        <v>22</v>
+        <v>7</v>
       </c>
     </row>
     <row r="417">
@@ -18503,7 +18503,7 @@
       </c>
       <c r="C417" s="11" t="inlineStr">
         <is>
-          <t>St-Laurent - Des Pins</t>
+          <t>Ste-Catherine est/ De Lorimier</t>
         </is>
       </c>
       <c r="D417" s="11" t="inlineStr">
@@ -18517,7 +18517,7 @@
         </is>
       </c>
       <c r="F417" s="11" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
     </row>
     <row r="418">
@@ -18533,12 +18533,12 @@
       </c>
       <c r="C418" s="11" t="inlineStr">
         <is>
-          <t>Ste-Catherine est/ De Lorimier</t>
+          <t>Ste-Catherine Ouest - Stanley</t>
         </is>
       </c>
       <c r="D418" s="11" t="inlineStr">
         <is>
-          <t>SAQ</t>
+          <t>SAQ Express</t>
         </is>
       </c>
       <c r="E418" s="11" t="inlineStr">
@@ -18547,7 +18547,7 @@
         </is>
       </c>
       <c r="F418" s="11" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
     <row r="419">
@@ -18563,12 +18563,12 @@
       </c>
       <c r="C419" s="11" t="inlineStr">
         <is>
-          <t>Ste-Catherine Ouest - Stanley</t>
+          <t>De la Montagne</t>
         </is>
       </c>
       <c r="D419" s="11" t="inlineStr">
         <is>
-          <t>SAQ Express</t>
+          <t>SAQ Sélection</t>
         </is>
       </c>
       <c r="E419" s="11" t="inlineStr">
@@ -18577,7 +18577,7 @@
         </is>
       </c>
       <c r="F419" s="11" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="420">
@@ -18593,12 +18593,12 @@
       </c>
       <c r="C420" s="11" t="inlineStr">
         <is>
-          <t>De la Montagne</t>
+          <t>Saint-Denis - Rachel</t>
         </is>
       </c>
       <c r="D420" s="11" t="inlineStr">
         <is>
-          <t>SAQ Sélection</t>
+          <t>SAQ</t>
         </is>
       </c>
       <c r="E420" s="11" t="inlineStr">
@@ -18607,7 +18607,7 @@
         </is>
       </c>
       <c r="F420" s="11" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="421">
@@ -18623,7 +18623,7 @@
       </c>
       <c r="C421" s="11" t="inlineStr">
         <is>
-          <t>Saint-Denis - Rachel</t>
+          <t>Faubourg Sainte-Catherine</t>
         </is>
       </c>
       <c r="D421" s="11" t="inlineStr">
@@ -18637,7 +18637,7 @@
         </is>
       </c>
       <c r="F421" s="11" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
     </row>
     <row r="422">
@@ -18667,7 +18667,7 @@
         </is>
       </c>
       <c r="F422" s="11" t="n">
-        <v>54</v>
+        <v>50</v>
       </c>
     </row>
     <row r="423">
@@ -18877,7 +18877,7 @@
         </is>
       </c>
       <c r="F429" s="11" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
     </row>
     <row r="430">
@@ -18997,7 +18997,7 @@
         </is>
       </c>
       <c r="F433" s="11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="434">
@@ -19177,7 +19177,7 @@
         </is>
       </c>
       <c r="F439" s="11" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="440">
@@ -19357,7 +19357,7 @@
         </is>
       </c>
       <c r="F445" s="11" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="446">
@@ -19747,7 +19747,7 @@
         </is>
       </c>
       <c r="F458" s="11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="459">
@@ -20347,7 +20347,7 @@
         </is>
       </c>
       <c r="F478" s="11" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="479">
@@ -20497,7 +20497,7 @@
         </is>
       </c>
       <c r="F483" s="11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="484">
@@ -20557,7 +20557,7 @@
         </is>
       </c>
       <c r="F485" s="11" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="486">
@@ -20707,7 +20707,7 @@
         </is>
       </c>
       <c r="F490" s="11" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="491">
@@ -20797,7 +20797,7 @@
         </is>
       </c>
       <c r="F493" s="11" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="494">
@@ -21157,7 +21157,7 @@
         </is>
       </c>
       <c r="F505" s="11" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="506">
@@ -21637,7 +21637,7 @@
         </is>
       </c>
       <c r="F521" s="11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="522">
@@ -21727,7 +21727,7 @@
         </is>
       </c>
       <c r="F524" s="11" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="525">
@@ -21757,7 +21757,7 @@
         </is>
       </c>
       <c r="F525" s="11" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="526">
@@ -21937,7 +21937,7 @@
         </is>
       </c>
       <c r="F531" s="11" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="532">
@@ -21967,7 +21967,7 @@
         </is>
       </c>
       <c r="F532" s="11" t="n">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="533">
@@ -22027,7 +22027,7 @@
         </is>
       </c>
       <c r="F534" s="11" t="n">
-        <v>62</v>
+        <v>59</v>
       </c>
     </row>
     <row r="535">
@@ -22087,7 +22087,7 @@
         </is>
       </c>
       <c r="F536" s="11" t="n">
-        <v>128</v>
+        <v>122</v>
       </c>
     </row>
     <row r="537">
@@ -22117,7 +22117,7 @@
         </is>
       </c>
       <c r="F537" s="11" t="n">
-        <v>133</v>
+        <v>115</v>
       </c>
     </row>
     <row r="538">
@@ -22207,7 +22207,7 @@
         </is>
       </c>
       <c r="F540" s="11" t="n">
-        <v>89</v>
+        <v>85</v>
       </c>
     </row>
     <row r="541">
@@ -22237,7 +22237,7 @@
         </is>
       </c>
       <c r="F541" s="11" t="n">
-        <v>230</v>
+        <v>226</v>
       </c>
     </row>
     <row r="542">
@@ -22267,7 +22267,7 @@
         </is>
       </c>
       <c r="F542" s="11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="543">
@@ -22927,7 +22927,7 @@
         </is>
       </c>
       <c r="F564" s="11" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="565">
@@ -23047,7 +23047,7 @@
         </is>
       </c>
       <c r="F568" s="11" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="569">
@@ -23317,7 +23317,7 @@
         </is>
       </c>
       <c r="F577" s="11" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="578">
@@ -23557,7 +23557,7 @@
         </is>
       </c>
       <c r="F585" s="11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="586">
@@ -23677,7 +23677,7 @@
         </is>
       </c>
       <c r="F589" s="11" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
     </row>
     <row r="590">
@@ -23707,7 +23707,7 @@
         </is>
       </c>
       <c r="F590" s="11" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="591">
@@ -23887,7 +23887,7 @@
         </is>
       </c>
       <c r="F596" s="11" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="597">
@@ -23933,12 +23933,12 @@
       </c>
       <c r="C598" s="11" t="inlineStr">
         <is>
-          <t>Ste-Catherine est/ De Lorimier</t>
+          <t>De la Montagne</t>
         </is>
       </c>
       <c r="D598" s="11" t="inlineStr">
         <is>
-          <t>SAQ</t>
+          <t>SAQ Sélection</t>
         </is>
       </c>
       <c r="E598" s="11" t="inlineStr">
@@ -23947,7 +23947,7 @@
         </is>
       </c>
       <c r="F598" s="11" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="599">
@@ -23963,12 +23963,12 @@
       </c>
       <c r="C599" s="11" t="inlineStr">
         <is>
-          <t>De la Montagne</t>
+          <t>Saint-Denis - Rachel</t>
         </is>
       </c>
       <c r="D599" s="11" t="inlineStr">
         <is>
-          <t>SAQ Sélection</t>
+          <t>SAQ</t>
         </is>
       </c>
       <c r="E599" s="11" t="inlineStr">
@@ -23977,7 +23977,7 @@
         </is>
       </c>
       <c r="F599" s="11" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="600">
@@ -23993,7 +23993,7 @@
       </c>
       <c r="C600" s="11" t="inlineStr">
         <is>
-          <t>Saint-Denis - Rachel</t>
+          <t>Faubourg Sainte-Catherine</t>
         </is>
       </c>
       <c r="D600" s="11" t="inlineStr">
@@ -24007,7 +24007,7 @@
         </is>
       </c>
       <c r="F600" s="11" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
     </row>
     <row r="601">
@@ -24023,7 +24023,7 @@
       </c>
       <c r="C601" s="11" t="inlineStr">
         <is>
-          <t>Faubourg Sainte-Catherine</t>
+          <t>Mont-Royal Ouest - Clark</t>
         </is>
       </c>
       <c r="D601" s="11" t="inlineStr">
@@ -24457,7 +24457,7 @@
         </is>
       </c>
       <c r="F615" s="11" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="616">
@@ -24607,7 +24607,7 @@
         </is>
       </c>
       <c r="F620" s="11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="621">
@@ -24697,7 +24697,7 @@
         </is>
       </c>
       <c r="F623" s="11" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="624">
@@ -24787,7 +24787,7 @@
         </is>
       </c>
       <c r="F626" s="11" t="n">
-        <v>196</v>
+        <v>193</v>
       </c>
     </row>
     <row r="627">
@@ -24847,7 +24847,7 @@
         </is>
       </c>
       <c r="F628" s="11" t="n">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="629">
@@ -24877,7 +24877,7 @@
         </is>
       </c>
       <c r="F629" s="11" t="n">
-        <v>76</v>
+        <v>73</v>
       </c>
     </row>
     <row r="630">
@@ -24907,7 +24907,7 @@
         </is>
       </c>
       <c r="F630" s="11" t="n">
-        <v>38</v>
+        <v>33</v>
       </c>
     </row>
     <row r="631">
@@ -24937,7 +24937,7 @@
         </is>
       </c>
       <c r="F631" s="11" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="632">
@@ -25733,12 +25733,12 @@
       </c>
       <c r="C658" s="11" t="inlineStr">
         <is>
-          <t>Mont-Royal Est - Mentana</t>
+          <t>Mont-Royal Est - Papineau</t>
         </is>
       </c>
       <c r="D658" s="11" t="inlineStr">
         <is>
-          <t>SAQ Express</t>
+          <t>SAQ Sélection</t>
         </is>
       </c>
       <c r="E658" s="11" t="inlineStr">
@@ -25747,7 +25747,7 @@
         </is>
       </c>
       <c r="F658" s="11" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
     </row>
     <row r="659">
@@ -25763,7 +25763,7 @@
       </c>
       <c r="C659" s="11" t="inlineStr">
         <is>
-          <t>Mont-Royal Est - Papineau</t>
+          <t>Marché Atwater</t>
         </is>
       </c>
       <c r="D659" s="11" t="inlineStr">
@@ -25777,7 +25777,7 @@
         </is>
       </c>
       <c r="F659" s="11" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
     </row>
     <row r="660">
@@ -25793,21 +25793,21 @@
       </c>
       <c r="C660" s="11" t="inlineStr">
         <is>
-          <t>Marché Atwater</t>
+          <t>Place Longueuil</t>
         </is>
       </c>
       <c r="D660" s="11" t="inlineStr">
         <is>
-          <t>SAQ Sélection</t>
+          <t>SAQ</t>
         </is>
       </c>
       <c r="E660" s="11" t="inlineStr">
         <is>
-          <t>Montréal</t>
+          <t>Longueuil</t>
         </is>
       </c>
       <c r="F660" s="11" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="661">
@@ -25823,21 +25823,21 @@
       </c>
       <c r="C661" s="11" t="inlineStr">
         <is>
-          <t>Place Longueuil</t>
+          <t>Ateliers Angus</t>
         </is>
       </c>
       <c r="D661" s="11" t="inlineStr">
         <is>
-          <t>SAQ</t>
+          <t>SAQ Sélection</t>
         </is>
       </c>
       <c r="E661" s="11" t="inlineStr">
         <is>
-          <t>Longueuil</t>
+          <t>Montréal</t>
         </is>
       </c>
       <c r="F661" s="11" t="n">
-        <v>2</v>
+        <v>35</v>
       </c>
     </row>
     <row r="662">
@@ -25867,7 +25867,7 @@
         </is>
       </c>
       <c r="F662" s="11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="663">
@@ -25927,7 +25927,7 @@
         </is>
       </c>
       <c r="F664" s="11" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="665">
@@ -26033,7 +26033,7 @@
       </c>
       <c r="C668" s="11" t="inlineStr">
         <is>
-          <t>Saint-Lambert - Boul. Sir-Wilfrid-Laurier</t>
+          <t>L'Île-des-Soeurs</t>
         </is>
       </c>
       <c r="D668" s="11" t="inlineStr">
@@ -26043,11 +26043,11 @@
       </c>
       <c r="E668" s="11" t="inlineStr">
         <is>
-          <t>Saint-Lambert</t>
+          <t>Montréal</t>
         </is>
       </c>
       <c r="F668" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="669">
@@ -26063,7 +26063,7 @@
       </c>
       <c r="C669" s="11" t="inlineStr">
         <is>
-          <t>L'Île-des-Soeurs</t>
+          <t>Beaubien - St-André</t>
         </is>
       </c>
       <c r="D669" s="11" t="inlineStr">
@@ -26077,7 +26077,7 @@
         </is>
       </c>
       <c r="F669" s="11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="670">
@@ -26093,12 +26093,12 @@
       </c>
       <c r="C670" s="11" t="inlineStr">
         <is>
-          <t>Beaubien - St-André</t>
+          <t>Jarry - Lajeunesse</t>
         </is>
       </c>
       <c r="D670" s="11" t="inlineStr">
         <is>
-          <t>SAQ Sélection</t>
+          <t>SAQ</t>
         </is>
       </c>
       <c r="E670" s="11" t="inlineStr">
@@ -26107,7 +26107,7 @@
         </is>
       </c>
       <c r="F670" s="11" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="671">
@@ -26123,12 +26123,12 @@
       </c>
       <c r="C671" s="11" t="inlineStr">
         <is>
-          <t>Jarry - Lajeunesse</t>
+          <t>Jean-Talon Est - Pie IX</t>
         </is>
       </c>
       <c r="D671" s="11" t="inlineStr">
         <is>
-          <t>SAQ</t>
+          <t>SAQ Sélection</t>
         </is>
       </c>
       <c r="E671" s="11" t="inlineStr">
@@ -26137,7 +26137,7 @@
         </is>
       </c>
       <c r="F671" s="11" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="672">
@@ -26257,7 +26257,7 @@
         </is>
       </c>
       <c r="F675" s="11" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="676">
@@ -26377,7 +26377,7 @@
         </is>
       </c>
       <c r="F679" s="11" t="n">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="680">
@@ -26437,7 +26437,7 @@
         </is>
       </c>
       <c r="F681" s="11" t="n">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="682">
@@ -26947,7 +26947,7 @@
         </is>
       </c>
       <c r="F698" s="11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="699">
@@ -27067,7 +27067,7 @@
         </is>
       </c>
       <c r="F702" s="11" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="703">
@@ -27247,7 +27247,7 @@
         </is>
       </c>
       <c r="F708" s="11" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
     </row>
     <row r="709">
@@ -27607,7 +27607,7 @@
         </is>
       </c>
       <c r="F720" s="11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="721">
@@ -27667,7 +27667,7 @@
         </is>
       </c>
       <c r="F722" s="11" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="723">
@@ -27847,7 +27847,7 @@
         </is>
       </c>
       <c r="F728" s="11" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="729">
@@ -27997,7 +27997,7 @@
         </is>
       </c>
       <c r="F733" s="11" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="734">
@@ -28117,7 +28117,7 @@
         </is>
       </c>
       <c r="F737" s="11" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="738">
@@ -28177,7 +28177,7 @@
         </is>
       </c>
       <c r="F739" s="11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="740">
@@ -28267,7 +28267,7 @@
         </is>
       </c>
       <c r="F742" s="11" t="n">
-        <v>55</v>
+        <v>51</v>
       </c>
     </row>
     <row r="743">
@@ -28477,7 +28477,7 @@
         </is>
       </c>
       <c r="F749" s="11" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="750">
@@ -28973,12 +28973,12 @@
       </c>
       <c r="C766" s="11" t="inlineStr">
         <is>
-          <t>Griffintown</t>
+          <t>De la Montagne</t>
         </is>
       </c>
       <c r="D766" s="11" t="inlineStr">
         <is>
-          <t>SAQ</t>
+          <t>SAQ Sélection</t>
         </is>
       </c>
       <c r="E766" s="11" t="inlineStr">
@@ -28987,7 +28987,7 @@
         </is>
       </c>
       <c r="F766" s="11" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="767">
@@ -29003,12 +29003,12 @@
       </c>
       <c r="C767" s="11" t="inlineStr">
         <is>
-          <t>De la Montagne</t>
+          <t>Exclusivement pour les restaurateurs</t>
         </is>
       </c>
       <c r="D767" s="11" t="inlineStr">
         <is>
-          <t>SAQ Sélection</t>
+          <t>SAQ Restauration</t>
         </is>
       </c>
       <c r="E767" s="11" t="inlineStr">
@@ -29017,7 +29017,7 @@
         </is>
       </c>
       <c r="F767" s="11" t="n">
-        <v>8</v>
+        <v>24</v>
       </c>
     </row>
     <row r="768">
@@ -29033,12 +29033,12 @@
       </c>
       <c r="C768" s="11" t="inlineStr">
         <is>
-          <t>Exclusivement pour les restaurateurs</t>
+          <t>Mont-Royal Est - Mentana</t>
         </is>
       </c>
       <c r="D768" s="11" t="inlineStr">
         <is>
-          <t>SAQ Restauration</t>
+          <t>SAQ Express</t>
         </is>
       </c>
       <c r="E768" s="11" t="inlineStr">
@@ -29047,7 +29047,7 @@
         </is>
       </c>
       <c r="F768" s="11" t="n">
-        <v>24</v>
+        <v>9</v>
       </c>
     </row>
     <row r="769">
@@ -29063,21 +29063,21 @@
       </c>
       <c r="C769" s="11" t="inlineStr">
         <is>
-          <t>Mont-Royal Est - Mentana</t>
+          <t>Saint-Lambert - Centre-ville</t>
         </is>
       </c>
       <c r="D769" s="11" t="inlineStr">
         <is>
-          <t>SAQ Express</t>
+          <t>SAQ</t>
         </is>
       </c>
       <c r="E769" s="11" t="inlineStr">
         <is>
-          <t>Montréal</t>
+          <t>Saint-Lambert</t>
         </is>
       </c>
       <c r="F769" s="11" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="770">
@@ -29093,17 +29093,17 @@
       </c>
       <c r="C770" s="11" t="inlineStr">
         <is>
-          <t>Saint-Lambert - Centre-ville</t>
+          <t>Marché Atwater</t>
         </is>
       </c>
       <c r="D770" s="11" t="inlineStr">
         <is>
-          <t>SAQ</t>
+          <t>SAQ Sélection</t>
         </is>
       </c>
       <c r="E770" s="11" t="inlineStr">
         <is>
-          <t>Saint-Lambert</t>
+          <t>Montréal</t>
         </is>
       </c>
       <c r="F770" s="11" t="n">
@@ -29123,21 +29123,21 @@
       </c>
       <c r="C771" s="11" t="inlineStr">
         <is>
-          <t>Marché Atwater</t>
+          <t>Place Longueuil</t>
         </is>
       </c>
       <c r="D771" s="11" t="inlineStr">
         <is>
-          <t>SAQ Sélection</t>
+          <t>SAQ</t>
         </is>
       </c>
       <c r="E771" s="11" t="inlineStr">
         <is>
-          <t>Montréal</t>
+          <t>Longueuil</t>
         </is>
       </c>
       <c r="F771" s="11" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
     </row>
     <row r="772">
@@ -29183,12 +29183,12 @@
       </c>
       <c r="C773" s="11" t="inlineStr">
         <is>
-          <t>De Maisonneuve - City Councillors</t>
+          <t>Halles de la Gare</t>
         </is>
       </c>
       <c r="D773" s="11" t="inlineStr">
         <is>
-          <t>SAQ Sélection</t>
+          <t>SAQ</t>
         </is>
       </c>
       <c r="E773" s="11" t="inlineStr">
@@ -29197,7 +29197,7 @@
         </is>
       </c>
       <c r="F773" s="11" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="774">
@@ -29213,7 +29213,7 @@
       </c>
       <c r="C774" s="11" t="inlineStr">
         <is>
-          <t>Halles de la Gare</t>
+          <t>La Cité - Les Galeries du Parc</t>
         </is>
       </c>
       <c r="D774" s="11" t="inlineStr">
@@ -29227,7 +29227,7 @@
         </is>
       </c>
       <c r="F774" s="11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="775">
@@ -29243,7 +29243,7 @@
       </c>
       <c r="C775" s="11" t="inlineStr">
         <is>
-          <t>La Cité - Les Galeries du Parc</t>
+          <t>Griffintown</t>
         </is>
       </c>
       <c r="D775" s="11" t="inlineStr">
@@ -29257,7 +29257,7 @@
         </is>
       </c>
       <c r="F775" s="11" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="776">
@@ -29273,7 +29273,7 @@
       </c>
       <c r="C776" s="11" t="inlineStr">
         <is>
-          <t>Griffintown</t>
+          <t>St-Laurent - Des Pins</t>
         </is>
       </c>
       <c r="D776" s="11" t="inlineStr">
@@ -29287,7 +29287,7 @@
         </is>
       </c>
       <c r="F776" s="11" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="777">
@@ -29303,7 +29303,7 @@
       </c>
       <c r="C777" s="11" t="inlineStr">
         <is>
-          <t>St-Laurent - Des Pins</t>
+          <t>Saint-Denis - Rachel</t>
         </is>
       </c>
       <c r="D777" s="11" t="inlineStr">
@@ -29317,7 +29317,7 @@
         </is>
       </c>
       <c r="F777" s="11" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="778">
@@ -29333,7 +29333,7 @@
       </c>
       <c r="C778" s="11" t="inlineStr">
         <is>
-          <t>Saint-Denis - Rachel</t>
+          <t>Faubourg Sainte-Catherine</t>
         </is>
       </c>
       <c r="D778" s="11" t="inlineStr">
@@ -29363,7 +29363,7 @@
       </c>
       <c r="C779" s="11" t="inlineStr">
         <is>
-          <t>Faubourg Sainte-Catherine</t>
+          <t>Mont-Royal Ouest - Clark</t>
         </is>
       </c>
       <c r="D779" s="11" t="inlineStr">
@@ -29377,7 +29377,7 @@
         </is>
       </c>
       <c r="F779" s="11" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="780">
@@ -29393,12 +29393,12 @@
       </c>
       <c r="C780" s="11" t="inlineStr">
         <is>
-          <t>Mont-Royal Ouest - Clark</t>
+          <t>Mont-Royal Est - Mentana</t>
         </is>
       </c>
       <c r="D780" s="11" t="inlineStr">
         <is>
-          <t>SAQ</t>
+          <t>SAQ Express</t>
         </is>
       </c>
       <c r="E780" s="11" t="inlineStr">
@@ -29407,7 +29407,7 @@
         </is>
       </c>
       <c r="F780" s="11" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="781">
@@ -29423,12 +29423,12 @@
       </c>
       <c r="C781" s="11" t="inlineStr">
         <is>
-          <t>Mont-Royal Est - Mentana</t>
+          <t>Sainte-Catherine Ouest - Lambert Closse</t>
         </is>
       </c>
       <c r="D781" s="11" t="inlineStr">
         <is>
-          <t>SAQ Express</t>
+          <t>SAQ</t>
         </is>
       </c>
       <c r="E781" s="11" t="inlineStr">
@@ -29437,7 +29437,7 @@
         </is>
       </c>
       <c r="F781" s="11" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="782">
@@ -29587,7 +29587,7 @@
         </is>
       </c>
       <c r="F786" s="11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="787">
@@ -29617,7 +29617,7 @@
         </is>
       </c>
       <c r="F787" s="11" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="788">
@@ -29707,7 +29707,7 @@
         </is>
       </c>
       <c r="F790" s="11" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="791">
@@ -29797,7 +29797,7 @@
         </is>
       </c>
       <c r="F793" s="11" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="794">
@@ -29947,7 +29947,7 @@
         </is>
       </c>
       <c r="F798" s="11" t="n">
-        <v>31</v>
+        <v>28</v>
       </c>
     </row>
     <row r="799">
@@ -30367,7 +30367,7 @@
         </is>
       </c>
       <c r="F812" s="11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="813">
@@ -30457,7 +30457,7 @@
         </is>
       </c>
       <c r="F815" s="11" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="816">
@@ -30487,7 +30487,7 @@
         </is>
       </c>
       <c r="F816" s="11" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="817">
@@ -30517,7 +30517,7 @@
         </is>
       </c>
       <c r="F817" s="11" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="818">
@@ -30637,7 +30637,7 @@
         </is>
       </c>
       <c r="F821" s="11" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="822">
@@ -30697,7 +30697,7 @@
         </is>
       </c>
       <c r="F823" s="11" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="824">
@@ -31087,7 +31087,7 @@
         </is>
       </c>
       <c r="F836" s="11" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="837">
@@ -31117,7 +31117,7 @@
         </is>
       </c>
       <c r="F837" s="11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="838">
@@ -31267,7 +31267,7 @@
         </is>
       </c>
       <c r="F842" s="11" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="843">
@@ -31357,7 +31357,7 @@
         </is>
       </c>
       <c r="F845" s="11" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="846">
@@ -31447,7 +31447,7 @@
         </is>
       </c>
       <c r="F848" s="11" t="n">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="849">
@@ -32737,7 +32737,7 @@
         </is>
       </c>
       <c r="F891" s="11" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="892">
@@ -33457,7 +33457,7 @@
         </is>
       </c>
       <c r="F915" s="11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="916">
@@ -33727,7 +33727,7 @@
         </is>
       </c>
       <c r="F924" s="11" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="925">
@@ -33937,7 +33937,7 @@
         </is>
       </c>
       <c r="F931" s="11" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="932">
@@ -33967,7 +33967,7 @@
         </is>
       </c>
       <c r="F932" s="11" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="933">
@@ -34057,7 +34057,7 @@
         </is>
       </c>
       <c r="F935" s="11" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="936">
@@ -34117,7 +34117,7 @@
         </is>
       </c>
       <c r="F937" s="11" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="938">
@@ -34207,7 +34207,7 @@
         </is>
       </c>
       <c r="F940" s="11" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="941">
@@ -34297,7 +34297,7 @@
         </is>
       </c>
       <c r="F943" s="11" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="944">
@@ -34387,7 +34387,7 @@
         </is>
       </c>
       <c r="F946" s="11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="947">
@@ -34477,7 +34477,7 @@
         </is>
       </c>
       <c r="F949" s="11" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="950">
@@ -34657,7 +34657,7 @@
         </is>
       </c>
       <c r="F955" s="11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="956">
@@ -35077,7 +35077,7 @@
         </is>
       </c>
       <c r="F969" s="11" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="970">
@@ -35257,7 +35257,7 @@
         </is>
       </c>
       <c r="F975" s="11" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="976">
@@ -35347,7 +35347,7 @@
         </is>
       </c>
       <c r="F978" s="11" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="979">
@@ -35377,7 +35377,7 @@
         </is>
       </c>
       <c r="F979" s="11" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="980">
@@ -35407,7 +35407,7 @@
         </is>
       </c>
       <c r="F980" s="11" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="981">
@@ -36727,7 +36727,7 @@
         </is>
       </c>
       <c r="F1024" s="11" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="1025">
@@ -36787,7 +36787,7 @@
         </is>
       </c>
       <c r="F1026" s="11" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="1027">
@@ -36877,7 +36877,7 @@
         </is>
       </c>
       <c r="F1029" s="11" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1030">
@@ -36967,7 +36967,7 @@
         </is>
       </c>
       <c r="F1032" s="11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1033">
@@ -37673,12 +37673,12 @@
       </c>
       <c r="C1056" s="11" t="inlineStr">
         <is>
-          <t>Rue Masson</t>
+          <t>Beaubien - St-André</t>
         </is>
       </c>
       <c r="D1056" s="11" t="inlineStr">
         <is>
-          <t>SAQ</t>
+          <t>SAQ Sélection</t>
         </is>
       </c>
       <c r="E1056" s="11" t="inlineStr">
@@ -37687,7 +37687,7 @@
         </is>
       </c>
       <c r="F1056" s="11" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="1057">
@@ -37703,7 +37703,7 @@
       </c>
       <c r="C1057" s="11" t="inlineStr">
         <is>
-          <t>Beaubien - St-André</t>
+          <t>Westmount</t>
         </is>
       </c>
       <c r="D1057" s="11" t="inlineStr">
@@ -37713,11 +37713,11 @@
       </c>
       <c r="E1057" s="11" t="inlineStr">
         <is>
-          <t>Montréal</t>
+          <t>Westmount</t>
         </is>
       </c>
       <c r="F1057" s="11" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1058">
@@ -37733,21 +37733,21 @@
       </c>
       <c r="C1058" s="11" t="inlineStr">
         <is>
-          <t>Westmount</t>
+          <t>Marché Jean-Talon</t>
         </is>
       </c>
       <c r="D1058" s="11" t="inlineStr">
         <is>
-          <t>SAQ Sélection</t>
+          <t>SAQ</t>
         </is>
       </c>
       <c r="E1058" s="11" t="inlineStr">
         <is>
-          <t>Westmount</t>
+          <t>Montréal</t>
         </is>
       </c>
       <c r="F1058" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1059">
@@ -37763,7 +37763,7 @@
       </c>
       <c r="C1059" s="11" t="inlineStr">
         <is>
-          <t>Marché Jean-Talon</t>
+          <t>N.D.G. - Rue Monkland</t>
         </is>
       </c>
       <c r="D1059" s="11" t="inlineStr">
@@ -37793,12 +37793,12 @@
       </c>
       <c r="C1060" s="11" t="inlineStr">
         <is>
-          <t>N.D.G. - Rue Monkland</t>
+          <t>Jean-Talon Est - Pie IX</t>
         </is>
       </c>
       <c r="D1060" s="11" t="inlineStr">
         <is>
-          <t>SAQ</t>
+          <t>SAQ Sélection</t>
         </is>
       </c>
       <c r="E1060" s="11" t="inlineStr">
@@ -37807,7 +37807,7 @@
         </is>
       </c>
       <c r="F1060" s="11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1061">
@@ -37823,7 +37823,7 @@
       </c>
       <c r="C1061" s="11" t="inlineStr">
         <is>
-          <t>Jean-Talon Est - Pie IX</t>
+          <t>Papineau - Crémazie</t>
         </is>
       </c>
       <c r="D1061" s="11" t="inlineStr">
@@ -37897,7 +37897,7 @@
         </is>
       </c>
       <c r="F1063" s="11" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1064">
@@ -38107,7 +38107,7 @@
         </is>
       </c>
       <c r="F1070" s="11" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="1071">
@@ -38393,21 +38393,21 @@
       </c>
       <c r="C1080" s="11" t="inlineStr">
         <is>
-          <t>Village Montpellier</t>
+          <t>Sherbrooke Est - Autoroute 25</t>
         </is>
       </c>
       <c r="D1080" s="11" t="inlineStr">
         <is>
-          <t>SAQ</t>
+          <t>SAQ Sélection</t>
         </is>
       </c>
       <c r="E1080" s="11" t="inlineStr">
         <is>
-          <t>Ville St-Laurent</t>
+          <t>Montréal</t>
         </is>
       </c>
       <c r="F1080" s="11" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
     </row>
     <row r="1081">
@@ -38423,7 +38423,7 @@
       </c>
       <c r="C1081" s="11" t="inlineStr">
         <is>
-          <t>Henri-Bourassa Ouest - Tanguay</t>
+          <t>Village Montpellier</t>
         </is>
       </c>
       <c r="D1081" s="11" t="inlineStr">
@@ -38433,11 +38433,11 @@
       </c>
       <c r="E1081" s="11" t="inlineStr">
         <is>
-          <t>Montréal</t>
+          <t>Ville St-Laurent</t>
         </is>
       </c>
       <c r="F1081" s="11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1082">
@@ -38647,7 +38647,7 @@
         </is>
       </c>
       <c r="F1088" s="11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1089">
@@ -39247,7 +39247,7 @@
         </is>
       </c>
       <c r="F1108" s="11" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="1109">
@@ -39487,7 +39487,7 @@
         </is>
       </c>
       <c r="F1116" s="11" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="1117">
@@ -39637,7 +39637,7 @@
         </is>
       </c>
       <c r="F1121" s="11" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="1122">
@@ -39727,7 +39727,7 @@
         </is>
       </c>
       <c r="F1124" s="11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1125">
@@ -39937,7 +39937,7 @@
         </is>
       </c>
       <c r="F1131" s="11" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1132">
@@ -39967,7 +39967,7 @@
         </is>
       </c>
       <c r="F1132" s="11" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="1133">
@@ -40267,7 +40267,7 @@
         </is>
       </c>
       <c r="F1142" s="11" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="1143">
@@ -40297,7 +40297,7 @@
         </is>
       </c>
       <c r="F1143" s="11" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="1144">
@@ -40357,7 +40357,7 @@
         </is>
       </c>
       <c r="F1145" s="11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1146">
@@ -40567,7 +40567,7 @@
         </is>
       </c>
       <c r="F1152" s="11" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="1153">
@@ -40613,7 +40613,7 @@
       </c>
       <c r="C1154" s="11" t="inlineStr">
         <is>
-          <t>Place D'Armes</t>
+          <t>Complexe Desjardins</t>
         </is>
       </c>
       <c r="D1154" s="11" t="inlineStr">
@@ -40627,7 +40627,7 @@
         </is>
       </c>
       <c r="F1154" s="11" t="n">
-        <v>2</v>
+        <v>212</v>
       </c>
     </row>
     <row r="1155">
@@ -40643,12 +40643,12 @@
       </c>
       <c r="C1155" s="11" t="inlineStr">
         <is>
-          <t>Complexe Desjardins</t>
+          <t>Place Dupuis</t>
         </is>
       </c>
       <c r="D1155" s="11" t="inlineStr">
         <is>
-          <t>SAQ</t>
+          <t>SAQ Express</t>
         </is>
       </c>
       <c r="E1155" s="11" t="inlineStr">
@@ -40657,7 +40657,7 @@
         </is>
       </c>
       <c r="F1155" s="11" t="n">
-        <v>212</v>
+        <v>20</v>
       </c>
     </row>
     <row r="1156">
@@ -40673,12 +40673,12 @@
       </c>
       <c r="C1156" s="11" t="inlineStr">
         <is>
-          <t>Place Dupuis</t>
+          <t>De Maisonneuve - City Councillors</t>
         </is>
       </c>
       <c r="D1156" s="11" t="inlineStr">
         <is>
-          <t>SAQ Express</t>
+          <t>SAQ Sélection</t>
         </is>
       </c>
       <c r="E1156" s="11" t="inlineStr">
@@ -40687,7 +40687,7 @@
         </is>
       </c>
       <c r="F1156" s="11" t="n">
-        <v>20</v>
+        <v>59</v>
       </c>
     </row>
     <row r="1157">
@@ -40703,12 +40703,12 @@
       </c>
       <c r="C1157" s="11" t="inlineStr">
         <is>
-          <t>De Maisonneuve - City Councillors</t>
+          <t>Halles de la Gare</t>
         </is>
       </c>
       <c r="D1157" s="11" t="inlineStr">
         <is>
-          <t>SAQ Sélection</t>
+          <t>SAQ</t>
         </is>
       </c>
       <c r="E1157" s="11" t="inlineStr">
@@ -40717,7 +40717,7 @@
         </is>
       </c>
       <c r="F1157" s="11" t="n">
-        <v>60</v>
+        <v>34</v>
       </c>
     </row>
     <row r="1158">
@@ -40733,7 +40733,7 @@
       </c>
       <c r="C1158" s="11" t="inlineStr">
         <is>
-          <t>Halles de la Gare</t>
+          <t>Centre Eaton</t>
         </is>
       </c>
       <c r="D1158" s="11" t="inlineStr">
@@ -40747,7 +40747,7 @@
         </is>
       </c>
       <c r="F1158" s="11" t="n">
-        <v>34</v>
+        <v>70</v>
       </c>
     </row>
     <row r="1159">
@@ -40763,7 +40763,7 @@
       </c>
       <c r="C1159" s="11" t="inlineStr">
         <is>
-          <t>Centre Eaton</t>
+          <t>La Cité - Les Galeries du Parc</t>
         </is>
       </c>
       <c r="D1159" s="11" t="inlineStr">
@@ -40777,7 +40777,7 @@
         </is>
       </c>
       <c r="F1159" s="11" t="n">
-        <v>74</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1160">
@@ -40793,7 +40793,7 @@
       </c>
       <c r="C1160" s="11" t="inlineStr">
         <is>
-          <t>La Cité - Les Galeries du Parc</t>
+          <t>Griffintown</t>
         </is>
       </c>
       <c r="D1160" s="11" t="inlineStr">
@@ -40807,7 +40807,7 @@
         </is>
       </c>
       <c r="F1160" s="11" t="n">
-        <v>4</v>
+        <v>28</v>
       </c>
     </row>
     <row r="1161">
@@ -40823,7 +40823,7 @@
       </c>
       <c r="C1161" s="11" t="inlineStr">
         <is>
-          <t>Griffintown</t>
+          <t>St-Laurent - Des Pins</t>
         </is>
       </c>
       <c r="D1161" s="11" t="inlineStr">
@@ -40837,7 +40837,7 @@
         </is>
       </c>
       <c r="F1161" s="11" t="n">
-        <v>29</v>
+        <v>9</v>
       </c>
     </row>
     <row r="1162">
@@ -40853,12 +40853,12 @@
       </c>
       <c r="C1162" s="11" t="inlineStr">
         <is>
-          <t>St-Laurent - Des Pins</t>
+          <t>Ste-Catherine Ouest - Stanley</t>
         </is>
       </c>
       <c r="D1162" s="11" t="inlineStr">
         <is>
-          <t>SAQ</t>
+          <t>SAQ Express</t>
         </is>
       </c>
       <c r="E1162" s="11" t="inlineStr">
@@ -40867,7 +40867,7 @@
         </is>
       </c>
       <c r="F1162" s="11" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1163">
@@ -40883,12 +40883,12 @@
       </c>
       <c r="C1163" s="11" t="inlineStr">
         <is>
-          <t>Ste-Catherine Ouest - Stanley</t>
+          <t>De la Montagne</t>
         </is>
       </c>
       <c r="D1163" s="11" t="inlineStr">
         <is>
-          <t>SAQ Express</t>
+          <t>SAQ Sélection</t>
         </is>
       </c>
       <c r="E1163" s="11" t="inlineStr">
@@ -40897,7 +40897,7 @@
         </is>
       </c>
       <c r="F1163" s="11" t="n">
-        <v>26</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1164">
@@ -41573,12 +41573,12 @@
       </c>
       <c r="C1186" s="11" t="inlineStr">
         <is>
-          <t>Sainte-Catherine Ouest - Lambert Closse</t>
+          <t>Ateliers Angus</t>
         </is>
       </c>
       <c r="D1186" s="11" t="inlineStr">
         <is>
-          <t>SAQ</t>
+          <t>SAQ Sélection</t>
         </is>
       </c>
       <c r="E1186" s="11" t="inlineStr">
@@ -41603,7 +41603,7 @@
       </c>
       <c r="C1187" s="11" t="inlineStr">
         <is>
-          <t>Ateliers Angus</t>
+          <t>Saint-Lambert - Boul. Sir-Wilfrid-Laurier</t>
         </is>
       </c>
       <c r="D1187" s="11" t="inlineStr">
@@ -41613,11 +41613,11 @@
       </c>
       <c r="E1187" s="11" t="inlineStr">
         <is>
-          <t>Montréal</t>
+          <t>Saint-Lambert</t>
         </is>
       </c>
       <c r="F1187" s="11" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1188">
@@ -41633,7 +41633,7 @@
       </c>
       <c r="C1188" s="11" t="inlineStr">
         <is>
-          <t>Saint-Lambert - Boul. Sir-Wilfrid-Laurier</t>
+          <t>L'Île-des-Soeurs</t>
         </is>
       </c>
       <c r="D1188" s="11" t="inlineStr">
@@ -41643,11 +41643,11 @@
       </c>
       <c r="E1188" s="11" t="inlineStr">
         <is>
-          <t>Saint-Lambert</t>
+          <t>Montréal</t>
         </is>
       </c>
       <c r="F1188" s="11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1189">
@@ -41663,7 +41663,7 @@
       </c>
       <c r="C1189" s="11" t="inlineStr">
         <is>
-          <t>L'Île-des-Soeurs</t>
+          <t>Beaubien - St-André</t>
         </is>
       </c>
       <c r="D1189" s="11" t="inlineStr">
@@ -41677,7 +41677,7 @@
         </is>
       </c>
       <c r="F1189" s="11" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
     </row>
     <row r="1190">
@@ -41693,12 +41693,12 @@
       </c>
       <c r="C1190" s="11" t="inlineStr">
         <is>
-          <t>Beaubien - St-André</t>
+          <t>Queen-Mary - Décarie</t>
         </is>
       </c>
       <c r="D1190" s="11" t="inlineStr">
         <is>
-          <t>SAQ Sélection</t>
+          <t>SAQ</t>
         </is>
       </c>
       <c r="E1190" s="11" t="inlineStr">
@@ -41707,7 +41707,7 @@
         </is>
       </c>
       <c r="F1190" s="11" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1191">
@@ -41723,7 +41723,7 @@
       </c>
       <c r="C1191" s="11" t="inlineStr">
         <is>
-          <t>Queen-Mary - Décarie</t>
+          <t>Jarry - Lajeunesse</t>
         </is>
       </c>
       <c r="D1191" s="11" t="inlineStr">
@@ -41737,7 +41737,7 @@
         </is>
       </c>
       <c r="F1191" s="11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1192">
@@ -41753,21 +41753,21 @@
       </c>
       <c r="C1192" s="11" t="inlineStr">
         <is>
-          <t>Jarry - Lajeunesse</t>
+          <t>Brossard - Taschereau/Adam</t>
         </is>
       </c>
       <c r="D1192" s="11" t="inlineStr">
         <is>
-          <t>SAQ</t>
+          <t>SAQ Sélection</t>
         </is>
       </c>
       <c r="E1192" s="11" t="inlineStr">
         <is>
-          <t>Montréal</t>
+          <t>Brossard</t>
         </is>
       </c>
       <c r="F1192" s="11" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="1193">
@@ -41783,21 +41783,21 @@
       </c>
       <c r="C1193" s="11" t="inlineStr">
         <is>
-          <t>Brossard - Taschereau/Adam</t>
+          <t>N.D.G. - Rue St-Jacques</t>
         </is>
       </c>
       <c r="D1193" s="11" t="inlineStr">
         <is>
-          <t>SAQ Sélection</t>
+          <t>SAQ</t>
         </is>
       </c>
       <c r="E1193" s="11" t="inlineStr">
         <is>
-          <t>Brossard</t>
+          <t>Montréal</t>
         </is>
       </c>
       <c r="F1193" s="11" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1194">
@@ -41917,7 +41917,7 @@
         </is>
       </c>
       <c r="F1197" s="11" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="1198">
@@ -42037,7 +42037,7 @@
         </is>
       </c>
       <c r="F1201" s="11" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="1202">
@@ -42997,7 +42997,7 @@
         </is>
       </c>
       <c r="F1233" s="11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1234">
@@ -43657,7 +43657,7 @@
         </is>
       </c>
       <c r="F1255" s="11" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="1256">
@@ -43687,7 +43687,7 @@
         </is>
       </c>
       <c r="F1256" s="11" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="1257">
@@ -44257,7 +44257,7 @@
         </is>
       </c>
       <c r="F1275" s="11" t="n">
-        <v>139</v>
+        <v>128</v>
       </c>
     </row>
     <row r="1276">
@@ -44317,7 +44317,7 @@
         </is>
       </c>
       <c r="F1277" s="11" t="n">
-        <v>138</v>
+        <v>136</v>
       </c>
     </row>
     <row r="1278">
@@ -44407,7 +44407,7 @@
         </is>
       </c>
       <c r="F1280" s="11" t="n">
-        <v>128</v>
+        <v>120</v>
       </c>
     </row>
     <row r="1281">
@@ -44437,7 +44437,7 @@
         </is>
       </c>
       <c r="F1281" s="11" t="n">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="1282">
@@ -44647,7 +44647,7 @@
         </is>
       </c>
       <c r="F1288" s="11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1289">
@@ -44977,7 +44977,7 @@
         </is>
       </c>
       <c r="F1299" s="11" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="1300">
@@ -45007,7 +45007,7 @@
         </is>
       </c>
       <c r="F1300" s="11" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1301">
@@ -45127,7 +45127,7 @@
         </is>
       </c>
       <c r="F1304" s="11" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1305">
@@ -45307,7 +45307,7 @@
         </is>
       </c>
       <c r="F1310" s="11" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="1311">
@@ -45727,7 +45727,7 @@
         </is>
       </c>
       <c r="F1324" s="11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1325">
@@ -45757,7 +45757,7 @@
         </is>
       </c>
       <c r="F1325" s="11" t="n">
-        <v>113</v>
+        <v>96</v>
       </c>
     </row>
     <row r="1326">
@@ -45817,7 +45817,7 @@
         </is>
       </c>
       <c r="F1327" s="11" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="1328">
@@ -45967,7 +45967,7 @@
         </is>
       </c>
       <c r="F1332" s="11" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="1333">
@@ -45997,7 +45997,7 @@
         </is>
       </c>
       <c r="F1333" s="11" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="1334">
@@ -46387,7 +46387,7 @@
         </is>
       </c>
       <c r="F1346" s="11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1347">
@@ -46477,7 +46477,7 @@
         </is>
       </c>
       <c r="F1349" s="11" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1350">
@@ -46957,7 +46957,7 @@
         </is>
       </c>
       <c r="F1365" s="11" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="1366">
@@ -47107,7 +47107,7 @@
         </is>
       </c>
       <c r="F1370" s="11" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="1371">
@@ -47617,7 +47617,7 @@
         </is>
       </c>
       <c r="F1387" s="11" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="1388">
@@ -47677,7 +47677,7 @@
         </is>
       </c>
       <c r="F1389" s="11" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="1390">
@@ -47767,7 +47767,7 @@
         </is>
       </c>
       <c r="F1392" s="11" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="1393">
@@ -47887,7 +47887,7 @@
         </is>
       </c>
       <c r="F1396" s="11" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="1397">
@@ -47917,7 +47917,7 @@
         </is>
       </c>
       <c r="F1397" s="11" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="1398">
@@ -48067,7 +48067,7 @@
         </is>
       </c>
       <c r="F1402" s="11" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="1403">
@@ -48157,7 +48157,7 @@
         </is>
       </c>
       <c r="F1405" s="11" t="n">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="1406">
@@ -48217,7 +48217,7 @@
         </is>
       </c>
       <c r="F1407" s="11" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="1408">
@@ -48337,7 +48337,7 @@
         </is>
       </c>
       <c r="F1411" s="11" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="1412">
@@ -48367,7 +48367,7 @@
         </is>
       </c>
       <c r="F1412" s="11" t="n">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="1413">
@@ -48397,7 +48397,7 @@
         </is>
       </c>
       <c r="F1413" s="11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1414">
@@ -48547,7 +48547,7 @@
         </is>
       </c>
       <c r="F1418" s="11" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="1419">
@@ -48907,7 +48907,7 @@
         </is>
       </c>
       <c r="F1430" s="11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1431">
@@ -49297,7 +49297,7 @@
         </is>
       </c>
       <c r="F1443" s="11" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1444">
@@ -49627,7 +49627,7 @@
         </is>
       </c>
       <c r="F1454" s="11" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="1455">
@@ -49897,7 +49897,7 @@
         </is>
       </c>
       <c r="F1463" s="11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1464">
@@ -50033,7 +50033,7 @@
       </c>
       <c r="C1468" s="11" t="inlineStr">
         <is>
-          <t>Saint-Lambert - Boul. Sir-Wilfrid-Laurier</t>
+          <t>Ateliers Angus</t>
         </is>
       </c>
       <c r="D1468" s="11" t="inlineStr">
@@ -50043,11 +50043,11 @@
       </c>
       <c r="E1468" s="11" t="inlineStr">
         <is>
-          <t>Saint-Lambert</t>
+          <t>Montréal</t>
         </is>
       </c>
       <c r="F1468" s="11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1469">
@@ -50063,21 +50063,21 @@
       </c>
       <c r="C1469" s="11" t="inlineStr">
         <is>
-          <t>Rue Masson</t>
+          <t>Saint-Lambert - Boul. Sir-Wilfrid-Laurier</t>
         </is>
       </c>
       <c r="D1469" s="11" t="inlineStr">
         <is>
-          <t>SAQ</t>
+          <t>SAQ Sélection</t>
         </is>
       </c>
       <c r="E1469" s="11" t="inlineStr">
         <is>
-          <t>Montréal</t>
+          <t>Saint-Lambert</t>
         </is>
       </c>
       <c r="F1469" s="11" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1470">
@@ -50093,12 +50093,12 @@
       </c>
       <c r="C1470" s="11" t="inlineStr">
         <is>
-          <t>Beaubien - St-André</t>
+          <t>Rue Masson</t>
         </is>
       </c>
       <c r="D1470" s="11" t="inlineStr">
         <is>
-          <t>SAQ Sélection</t>
+          <t>SAQ</t>
         </is>
       </c>
       <c r="E1470" s="11" t="inlineStr">
@@ -50107,7 +50107,7 @@
         </is>
       </c>
       <c r="F1470" s="11" t="n">
-        <v>23</v>
+        <v>14</v>
       </c>
     </row>
     <row r="1471">
@@ -50123,7 +50123,7 @@
       </c>
       <c r="C1471" s="11" t="inlineStr">
         <is>
-          <t>Longueuil - Boul. Roland-Therrien</t>
+          <t>Beaubien - St-André</t>
         </is>
       </c>
       <c r="D1471" s="11" t="inlineStr">
@@ -50133,11 +50133,11 @@
       </c>
       <c r="E1471" s="11" t="inlineStr">
         <is>
-          <t>Longueuil</t>
+          <t>Montréal</t>
         </is>
       </c>
       <c r="F1471" s="11" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
     </row>
     <row r="1472">
@@ -50153,7 +50153,7 @@
       </c>
       <c r="C1472" s="11" t="inlineStr">
         <is>
-          <t>Quartier DIX30</t>
+          <t>Longueuil - Boul. Roland-Therrien</t>
         </is>
       </c>
       <c r="D1472" s="11" t="inlineStr">
@@ -50163,11 +50163,11 @@
       </c>
       <c r="E1472" s="11" t="inlineStr">
         <is>
-          <t>Brossard</t>
+          <t>Longueuil</t>
         </is>
       </c>
       <c r="F1472" s="11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1473">
@@ -50183,17 +50183,17 @@
       </c>
       <c r="C1473" s="11" t="inlineStr">
         <is>
-          <t>Saint-Constant</t>
+          <t>Quartier DIX30</t>
         </is>
       </c>
       <c r="D1473" s="11" t="inlineStr">
         <is>
-          <t>SAQ</t>
+          <t>SAQ Sélection</t>
         </is>
       </c>
       <c r="E1473" s="11" t="inlineStr">
         <is>
-          <t>St-Constant</t>
+          <t>Brossard</t>
         </is>
       </c>
       <c r="F1473" s="11" t="n">
@@ -50497,7 +50497,7 @@
         </is>
       </c>
       <c r="F1483" s="11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1484">
@@ -50527,7 +50527,7 @@
         </is>
       </c>
       <c r="F1484" s="11" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1485">
@@ -50543,12 +50543,12 @@
       </c>
       <c r="C1485" s="11" t="inlineStr">
         <is>
-          <t>De Maisonneuve - City Councillors</t>
+          <t>Place Dupuis</t>
         </is>
       </c>
       <c r="D1485" s="11" t="inlineStr">
         <is>
-          <t>SAQ Sélection</t>
+          <t>SAQ Express</t>
         </is>
       </c>
       <c r="E1485" s="11" t="inlineStr">
@@ -50557,7 +50557,7 @@
         </is>
       </c>
       <c r="F1485" s="11" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
     </row>
     <row r="1486">
@@ -50573,12 +50573,12 @@
       </c>
       <c r="C1486" s="11" t="inlineStr">
         <is>
-          <t>Halles de la Gare</t>
+          <t>De Maisonneuve - City Councillors</t>
         </is>
       </c>
       <c r="D1486" s="11" t="inlineStr">
         <is>
-          <t>SAQ</t>
+          <t>SAQ Sélection</t>
         </is>
       </c>
       <c r="E1486" s="11" t="inlineStr">
@@ -50587,7 +50587,7 @@
         </is>
       </c>
       <c r="F1486" s="11" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1487">
@@ -50603,7 +50603,7 @@
       </c>
       <c r="C1487" s="11" t="inlineStr">
         <is>
-          <t>La Cité - Les Galeries du Parc</t>
+          <t>Halles de la Gare</t>
         </is>
       </c>
       <c r="D1487" s="11" t="inlineStr">
@@ -50617,7 +50617,7 @@
         </is>
       </c>
       <c r="F1487" s="11" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
     </row>
     <row r="1488">
@@ -50633,7 +50633,7 @@
       </c>
       <c r="C1488" s="11" t="inlineStr">
         <is>
-          <t>Griffintown</t>
+          <t>La Cité - Les Galeries du Parc</t>
         </is>
       </c>
       <c r="D1488" s="11" t="inlineStr">
@@ -50647,7 +50647,7 @@
         </is>
       </c>
       <c r="F1488" s="11" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1489">
@@ -50663,7 +50663,7 @@
       </c>
       <c r="C1489" s="11" t="inlineStr">
         <is>
-          <t>St-Laurent - Des Pins</t>
+          <t>Griffintown</t>
         </is>
       </c>
       <c r="D1489" s="11" t="inlineStr">
@@ -50677,7 +50677,7 @@
         </is>
       </c>
       <c r="F1489" s="11" t="n">
-        <v>22</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1490">
@@ -50693,7 +50693,7 @@
       </c>
       <c r="C1490" s="11" t="inlineStr">
         <is>
-          <t>Ste-Catherine est/ De Lorimier</t>
+          <t>St-Laurent - Des Pins</t>
         </is>
       </c>
       <c r="D1490" s="11" t="inlineStr">
@@ -50707,7 +50707,7 @@
         </is>
       </c>
       <c r="F1490" s="11" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
     </row>
     <row r="1491">
@@ -50723,7 +50723,7 @@
       </c>
       <c r="C1491" s="11" t="inlineStr">
         <is>
-          <t>Saint-Denis - Rachel</t>
+          <t>Ste-Catherine est/ De Lorimier</t>
         </is>
       </c>
       <c r="D1491" s="11" t="inlineStr">
@@ -50737,7 +50737,7 @@
         </is>
       </c>
       <c r="F1491" s="11" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
     </row>
     <row r="1492">
@@ -50753,7 +50753,7 @@
       </c>
       <c r="C1492" s="11" t="inlineStr">
         <is>
-          <t>Faubourg Sainte-Catherine</t>
+          <t>Saint-Denis - Rachel</t>
         </is>
       </c>
       <c r="D1492" s="11" t="inlineStr">
@@ -50767,7 +50767,7 @@
         </is>
       </c>
       <c r="F1492" s="11" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
     </row>
     <row r="1493">
@@ -50783,7 +50783,7 @@
       </c>
       <c r="C1493" s="11" t="inlineStr">
         <is>
-          <t>Mont-Royal Ouest - Clark</t>
+          <t>Faubourg Sainte-Catherine</t>
         </is>
       </c>
       <c r="D1493" s="11" t="inlineStr">
@@ -50797,7 +50797,7 @@
         </is>
       </c>
       <c r="F1493" s="11" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
     </row>
     <row r="1494">
@@ -51097,7 +51097,7 @@
         </is>
       </c>
       <c r="F1503" s="11" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1504">
@@ -51277,7 +51277,7 @@
         </is>
       </c>
       <c r="F1509" s="11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="1510">
@@ -51907,7 +51907,7 @@
         </is>
       </c>
       <c r="F1530" s="11" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="1531">
@@ -52057,7 +52057,7 @@
         </is>
       </c>
       <c r="F1535" s="11" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
     </row>
     <row r="1536">
@@ -52147,7 +52147,7 @@
         </is>
       </c>
       <c r="F1538" s="11" t="n">
-        <v>223</v>
+        <v>217</v>
       </c>
     </row>
     <row r="1539">
@@ -52777,7 +52777,7 @@
         </is>
       </c>
       <c r="F1559" s="11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1560">
@@ -52837,7 +52837,7 @@
         </is>
       </c>
       <c r="F1561" s="11" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="1562">
@@ -53767,7 +53767,7 @@
         </is>
       </c>
       <c r="F1592" s="11" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="1593">
@@ -53857,7 +53857,7 @@
         </is>
       </c>
       <c r="F1595" s="11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1596">
@@ -54007,7 +54007,7 @@
         </is>
       </c>
       <c r="F1600" s="11" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="1601">
@@ -54907,7 +54907,7 @@
         </is>
       </c>
       <c r="F1630" s="11" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="1631">
@@ -54997,7 +54997,7 @@
         </is>
       </c>
       <c r="F1633" s="11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1634">
@@ -55207,7 +55207,7 @@
         </is>
       </c>
       <c r="F1640" s="11" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="1641">
@@ -56077,7 +56077,7 @@
         </is>
       </c>
       <c r="F1669" s="11" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1670">
@@ -56317,7 +56317,7 @@
         </is>
       </c>
       <c r="F1677" s="11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="1678">
@@ -56347,7 +56347,7 @@
         </is>
       </c>
       <c r="F1678" s="11" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1679">
@@ -57277,7 +57277,7 @@
         </is>
       </c>
       <c r="F1709" s="11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="1710">
@@ -57697,7 +57697,7 @@
         </is>
       </c>
       <c r="F1723" s="11" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="1724">
@@ -57757,7 +57757,7 @@
         </is>
       </c>
       <c r="F1725" s="11" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="1726">
@@ -58027,7 +58027,7 @@
         </is>
       </c>
       <c r="F1734" s="11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1735">
@@ -58867,7 +58867,7 @@
         </is>
       </c>
       <c r="F1762" s="11" t="n">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="1763">
@@ -59107,7 +59107,7 @@
         </is>
       </c>
       <c r="F1770" s="11" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="1771">
@@ -59407,7 +59407,7 @@
         </is>
       </c>
       <c r="F1780" s="11" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="1781">
@@ -61537,7 +61537,7 @@
         </is>
       </c>
       <c r="F1851" s="11" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="1852">
@@ -62077,7 +62077,7 @@
         </is>
       </c>
       <c r="F1869" s="11" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="1870">
@@ -62827,7 +62827,7 @@
         </is>
       </c>
       <c r="F1894" s="11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1895">
@@ -63007,7 +63007,7 @@
         </is>
       </c>
       <c r="F1900" s="11" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1901">
@@ -64117,7 +64117,7 @@
         </is>
       </c>
       <c r="F1937" s="11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1938">
@@ -64327,7 +64327,7 @@
         </is>
       </c>
       <c r="F1944" s="11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="1945">
@@ -64357,7 +64357,7 @@
         </is>
       </c>
       <c r="F1945" s="11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1946">
@@ -64507,7 +64507,7 @@
         </is>
       </c>
       <c r="F1950" s="11" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="1951">
@@ -64567,7 +64567,7 @@
         </is>
       </c>
       <c r="F1952" s="11" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="1953">
@@ -65317,7 +65317,7 @@
         </is>
       </c>
       <c r="F1977" s="11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="1978">
@@ -66217,7 +66217,7 @@
         </is>
       </c>
       <c r="F2007" s="11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="2008">
@@ -67973,21 +67973,21 @@
       </c>
       <c r="C2066" s="11" t="inlineStr">
         <is>
-          <t>Dépôt Laurentides</t>
+          <t>Mirabel - Saint-Janvier</t>
         </is>
       </c>
       <c r="D2066" s="11" t="inlineStr">
         <is>
-          <t>SAQ Dépôt</t>
+          <t>SAQ</t>
         </is>
       </c>
       <c r="E2066" s="11" t="inlineStr">
         <is>
-          <t>Blainville</t>
+          <t>Mirabel</t>
         </is>
       </c>
       <c r="F2066" s="11" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="2067">
@@ -68003,21 +68003,21 @@
       </c>
       <c r="C2067" s="11" t="inlineStr">
         <is>
-          <t>Mirabel - Saint-Janvier</t>
+          <t>Dépôt Vaudreuil-Soulanges</t>
         </is>
       </c>
       <c r="D2067" s="11" t="inlineStr">
         <is>
-          <t>SAQ</t>
+          <t>SAQ Dépôt</t>
         </is>
       </c>
       <c r="E2067" s="11" t="inlineStr">
         <is>
-          <t>Mirabel</t>
+          <t>Vaudreuil-Dorion</t>
         </is>
       </c>
       <c r="F2067" s="11" t="n">
-        <v>6</v>
+        <v>45</v>
       </c>
     </row>
     <row r="2068">
@@ -68033,21 +68033,21 @@
       </c>
       <c r="C2068" s="11" t="inlineStr">
         <is>
-          <t>Dépôt Vaudreuil-Soulanges</t>
+          <t>Sainte-Agathe-des-Monts</t>
         </is>
       </c>
       <c r="D2068" s="11" t="inlineStr">
         <is>
-          <t>SAQ Dépôt</t>
+          <t>SAQ Sélection</t>
         </is>
       </c>
       <c r="E2068" s="11" t="inlineStr">
         <is>
-          <t>Vaudreuil-Dorion</t>
+          <t>Sainte-Agathe-des-Monts</t>
         </is>
       </c>
       <c r="F2068" s="11" t="n">
-        <v>45</v>
+        <v>36</v>
       </c>
     </row>
     <row r="2069">
@@ -68063,7 +68063,7 @@
       </c>
       <c r="C2069" s="11" t="inlineStr">
         <is>
-          <t>Sainte-Agathe-des-Monts</t>
+          <t>Sherbrooke - J.-Cartier Sud/King Ouest</t>
         </is>
       </c>
       <c r="D2069" s="11" t="inlineStr">
@@ -68073,11 +68073,11 @@
       </c>
       <c r="E2069" s="11" t="inlineStr">
         <is>
-          <t>Sainte-Agathe-des-Monts</t>
+          <t>Sherbrooke</t>
         </is>
       </c>
       <c r="F2069" s="11" t="n">
-        <v>36</v>
+        <v>2</v>
       </c>
     </row>
     <row r="2070">
@@ -68093,21 +68093,21 @@
       </c>
       <c r="C2070" s="11" t="inlineStr">
         <is>
-          <t>Sherbrooke - J.-Cartier Sud/King Ouest</t>
+          <t>La Baie</t>
         </is>
       </c>
       <c r="D2070" s="11" t="inlineStr">
         <is>
-          <t>SAQ Sélection</t>
+          <t>SAQ</t>
         </is>
       </c>
       <c r="E2070" s="11" t="inlineStr">
         <is>
-          <t>Sherbrooke</t>
+          <t>La Baie</t>
         </is>
       </c>
       <c r="F2070" s="11" t="n">
-        <v>2</v>
+        <v>35</v>
       </c>
     </row>
     <row r="2071">
@@ -68123,37 +68123,37 @@
       </c>
       <c r="C2071" s="11" t="inlineStr">
         <is>
-          <t>La Baie</t>
+          <t>Rouyn-Noranda</t>
         </is>
       </c>
       <c r="D2071" s="11" t="inlineStr">
         <is>
-          <t>SAQ</t>
+          <t>SAQ Sélection</t>
         </is>
       </c>
       <c r="E2071" s="11" t="inlineStr">
         <is>
-          <t>La Baie</t>
+          <t>Rouyn-Noranda</t>
         </is>
       </c>
       <c r="F2071" s="11" t="n">
-        <v>35</v>
+        <v>4</v>
       </c>
     </row>
     <row r="2072">
       <c r="A2072" s="11" t="inlineStr">
         <is>
-          <t>15149211</t>
+          <t>15299480</t>
         </is>
       </c>
       <c r="B2072" s="11" t="inlineStr">
         <is>
-          <t>Palm Bay Ananas Citron Vert Zero Sucre (4 x 355 ml)</t>
+          <t>Mike's Hard Lemonade Limonade Classique</t>
         </is>
       </c>
       <c r="C2072" s="11" t="inlineStr">
         <is>
-          <t>Rouyn-Noranda</t>
+          <t>Beaubien - St-André</t>
         </is>
       </c>
       <c r="D2072" s="11" t="inlineStr">
@@ -68163,11 +68163,11 @@
       </c>
       <c r="E2072" s="11" t="inlineStr">
         <is>
-          <t>Rouyn-Noranda</t>
+          <t>Montréal</t>
         </is>
       </c>
       <c r="F2072" s="11" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
     </row>
     <row r="2073">
@@ -68183,7 +68183,7 @@
       </c>
       <c r="C2073" s="11" t="inlineStr">
         <is>
-          <t>Beaubien - St-André</t>
+          <t>Pierrefonds - Boul. St-Jean</t>
         </is>
       </c>
       <c r="D2073" s="11" t="inlineStr">
@@ -68197,7 +68197,7 @@
         </is>
       </c>
       <c r="F2073" s="11" t="n">
-        <v>25</v>
+        <v>2</v>
       </c>
     </row>
     <row r="2074">
@@ -68213,7 +68213,7 @@
       </c>
       <c r="C2074" s="11" t="inlineStr">
         <is>
-          <t>Pierrefonds - Boul. St-Jean</t>
+          <t>Mont-Tremblant - Saint-Jovite</t>
         </is>
       </c>
       <c r="D2074" s="11" t="inlineStr">
@@ -68223,7 +68223,7 @@
       </c>
       <c r="E2074" s="11" t="inlineStr">
         <is>
-          <t>Montréal</t>
+          <t>Mont-Tremblant</t>
         </is>
       </c>
       <c r="F2074" s="11" t="n">
@@ -68243,21 +68243,21 @@
       </c>
       <c r="C2075" s="11" t="inlineStr">
         <is>
-          <t>Mont-Tremblant - Saint-Jovite</t>
+          <t>Québec - Ch. Saint-Louis</t>
         </is>
       </c>
       <c r="D2075" s="11" t="inlineStr">
         <is>
-          <t>SAQ Sélection</t>
+          <t>SAQ</t>
         </is>
       </c>
       <c r="E2075" s="11" t="inlineStr">
         <is>
-          <t>Mont-Tremblant</t>
+          <t>Québec</t>
         </is>
       </c>
       <c r="F2075" s="11" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="2076">
@@ -68273,7 +68273,7 @@
       </c>
       <c r="C2076" s="11" t="inlineStr">
         <is>
-          <t>Québec - Ch. Saint-Louis</t>
+          <t>Vanier</t>
         </is>
       </c>
       <c r="D2076" s="11" t="inlineStr">
@@ -68287,7 +68287,7 @@
         </is>
       </c>
       <c r="F2076" s="11" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="2077">
@@ -68303,7 +68303,7 @@
       </c>
       <c r="C2077" s="11" t="inlineStr">
         <is>
-          <t>Vanier</t>
+          <t>Beauport - Av. Nordique</t>
         </is>
       </c>
       <c r="D2077" s="11" t="inlineStr">
@@ -68313,11 +68313,11 @@
       </c>
       <c r="E2077" s="11" t="inlineStr">
         <is>
-          <t>Québec</t>
+          <t>Beauport</t>
         </is>
       </c>
       <c r="F2077" s="11" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="2078">
@@ -68333,7 +68333,7 @@
       </c>
       <c r="C2078" s="11" t="inlineStr">
         <is>
-          <t>Beauport - Av. Nordique</t>
+          <t>Forestville</t>
         </is>
       </c>
       <c r="D2078" s="11" t="inlineStr">
@@ -68343,11 +68343,11 @@
       </c>
       <c r="E2078" s="11" t="inlineStr">
         <is>
-          <t>Beauport</t>
+          <t>Forestville</t>
         </is>
       </c>
       <c r="F2078" s="11" t="n">
-        <v>6</v>
+        <v>31</v>
       </c>
     </row>
     <row r="2079">
@@ -68363,7 +68363,7 @@
       </c>
       <c r="C2079" s="11" t="inlineStr">
         <is>
-          <t>Forestville</t>
+          <t>Pointe-à-la-Croix</t>
         </is>
       </c>
       <c r="D2079" s="11" t="inlineStr">
@@ -68373,41 +68373,41 @@
       </c>
       <c r="E2079" s="11" t="inlineStr">
         <is>
-          <t>Forestville</t>
+          <t>Pointe-à-la-Croix</t>
         </is>
       </c>
       <c r="F2079" s="11" t="n">
-        <v>31</v>
+        <v>40</v>
       </c>
     </row>
     <row r="2080">
       <c r="A2080" s="11" t="inlineStr">
         <is>
-          <t>15299480</t>
+          <t>15021461</t>
         </is>
       </c>
       <c r="B2080" s="11" t="inlineStr">
         <is>
-          <t>Mike's Hard Lemonade Limonade Classique</t>
+          <t>Kopparberg Peche sans alcool (4 x 500 ml)</t>
         </is>
       </c>
       <c r="C2080" s="11" t="inlineStr">
         <is>
-          <t>Pointe-à-la-Croix</t>
+          <t>Exclusivement pour les restaurateurs</t>
         </is>
       </c>
       <c r="D2080" s="11" t="inlineStr">
         <is>
-          <t>SAQ</t>
+          <t>SAQ Restauration</t>
         </is>
       </c>
       <c r="E2080" s="11" t="inlineStr">
         <is>
-          <t>Pointe-à-la-Croix</t>
+          <t>Montréal</t>
         </is>
       </c>
       <c r="F2080" s="11" t="n">
-        <v>40</v>
+        <v>3</v>
       </c>
     </row>
     <row r="2081">
@@ -68423,21 +68423,21 @@
       </c>
       <c r="C2081" s="11" t="inlineStr">
         <is>
-          <t>Exclusivement pour les restaurateurs</t>
+          <t>Village Montpellier</t>
         </is>
       </c>
       <c r="D2081" s="11" t="inlineStr">
         <is>
-          <t>SAQ Restauration</t>
+          <t>SAQ</t>
         </is>
       </c>
       <c r="E2081" s="11" t="inlineStr">
         <is>
-          <t>Montréal</t>
+          <t>Ville St-Laurent</t>
         </is>
       </c>
       <c r="F2081" s="11" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="2082">
@@ -68453,21 +68453,21 @@
       </c>
       <c r="C2082" s="11" t="inlineStr">
         <is>
-          <t>Village Montpellier</t>
+          <t>Vaudreuil</t>
         </is>
       </c>
       <c r="D2082" s="11" t="inlineStr">
         <is>
-          <t>SAQ</t>
+          <t>SAQ Sélection</t>
         </is>
       </c>
       <c r="E2082" s="11" t="inlineStr">
         <is>
-          <t>Ville St-Laurent</t>
+          <t>Vaudreuil-Dorion</t>
         </is>
       </c>
       <c r="F2082" s="11" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="2083">
@@ -68483,67 +68483,67 @@
       </c>
       <c r="C2083" s="11" t="inlineStr">
         <is>
-          <t>Vaudreuil</t>
+          <t>Amqui</t>
         </is>
       </c>
       <c r="D2083" s="11" t="inlineStr">
         <is>
-          <t>SAQ Sélection</t>
+          <t>SAQ</t>
         </is>
       </c>
       <c r="E2083" s="11" t="inlineStr">
         <is>
-          <t>Vaudreuil-Dorion</t>
+          <t>Amqui</t>
         </is>
       </c>
       <c r="F2083" s="11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="2084">
       <c r="A2084" s="11" t="inlineStr">
         <is>
-          <t>15021461</t>
+          <t>11440255</t>
         </is>
       </c>
       <c r="B2084" s="11" t="inlineStr">
         <is>
-          <t>Kopparberg Peche sans alcool (4 x 500 ml)</t>
+          <t>Mott's Clamato Caesar Classique (946 ml)</t>
         </is>
       </c>
       <c r="C2084" s="11" t="inlineStr">
         <is>
-          <t>Amqui</t>
+          <t>Val d'Or</t>
         </is>
       </c>
       <c r="D2084" s="11" t="inlineStr">
         <is>
-          <t>SAQ</t>
+          <t>SAQ Sélection</t>
         </is>
       </c>
       <c r="E2084" s="11" t="inlineStr">
         <is>
-          <t>Amqui</t>
+          <t>Val-d'Or</t>
         </is>
       </c>
       <c r="F2084" s="11" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="2085">
       <c r="A2085" s="11" t="inlineStr">
         <is>
-          <t>11440255</t>
+          <t>15538743</t>
         </is>
       </c>
       <c r="B2085" s="11" t="inlineStr">
         <is>
-          <t>Mott's Clamato Caesar Classique (946 ml)</t>
+          <t>Carabins Gin Limonade Framboise Bleue (4 x 355 ml)</t>
         </is>
       </c>
       <c r="C2085" s="11" t="inlineStr">
         <is>
-          <t>Val d'Or</t>
+          <t>Sorel</t>
         </is>
       </c>
       <c r="D2085" s="11" t="inlineStr">
@@ -68553,11 +68553,11 @@
       </c>
       <c r="E2085" s="11" t="inlineStr">
         <is>
-          <t>Val-d'Or</t>
+          <t>Sorel-Tracy</t>
         </is>
       </c>
       <c r="F2085" s="11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="2086">
@@ -68573,7 +68573,7 @@
       </c>
       <c r="C2086" s="11" t="inlineStr">
         <is>
-          <t>Sorel</t>
+          <t>Galeries de la Capitale</t>
         </is>
       </c>
       <c r="D2086" s="11" t="inlineStr">
@@ -68583,32 +68583,32 @@
       </c>
       <c r="E2086" s="11" t="inlineStr">
         <is>
-          <t>Sorel-Tracy</t>
+          <t>Québec</t>
         </is>
       </c>
       <c r="F2086" s="11" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="2087">
       <c r="A2087" s="11" t="inlineStr">
         <is>
-          <t>15538743</t>
+          <t>15125957</t>
         </is>
       </c>
       <c r="B2087" s="11" t="inlineStr">
         <is>
-          <t>Carabins Gin Limonade Framboise Bleue (4 x 355 ml)</t>
+          <t>Kopparberg Citron sans alcool (4 x 500 ml)</t>
         </is>
       </c>
       <c r="C2087" s="11" t="inlineStr">
         <is>
-          <t>Galeries de la Capitale</t>
+          <t>Dépôt Québec</t>
         </is>
       </c>
       <c r="D2087" s="11" t="inlineStr">
         <is>
-          <t>SAQ Sélection</t>
+          <t>SAQ Dépôt</t>
         </is>
       </c>
       <c r="E2087" s="11" t="inlineStr">
@@ -68617,37 +68617,37 @@
         </is>
       </c>
       <c r="F2087" s="11" t="n">
-        <v>6</v>
+        <v>272</v>
       </c>
     </row>
     <row r="2088">
       <c r="A2088" s="11" t="inlineStr">
         <is>
-          <t>15125957</t>
+          <t>14960213</t>
         </is>
       </c>
       <c r="B2088" s="11" t="inlineStr">
         <is>
-          <t>Kopparberg Citron sans alcool (4 x 500 ml)</t>
+          <t>Kopparberg Poire 0% (4 x 500 ml)</t>
         </is>
       </c>
       <c r="C2088" s="11" t="inlineStr">
         <is>
-          <t>Dépôt Québec</t>
+          <t>Galeries Orford</t>
         </is>
       </c>
       <c r="D2088" s="11" t="inlineStr">
         <is>
-          <t>SAQ Dépôt</t>
+          <t>SAQ</t>
         </is>
       </c>
       <c r="E2088" s="11" t="inlineStr">
         <is>
-          <t>Québec</t>
+          <t>Magog</t>
         </is>
       </c>
       <c r="F2088" s="11" t="n">
-        <v>272</v>
+        <v>40</v>
       </c>
     </row>
     <row r="2089">
@@ -68663,51 +68663,51 @@
       </c>
       <c r="C2089" s="11" t="inlineStr">
         <is>
-          <t>Galeries Orford</t>
+          <t>Dépôt Québec</t>
         </is>
       </c>
       <c r="D2089" s="11" t="inlineStr">
         <is>
-          <t>SAQ</t>
+          <t>SAQ Dépôt</t>
         </is>
       </c>
       <c r="E2089" s="11" t="inlineStr">
         <is>
-          <t>Magog</t>
+          <t>Québec</t>
         </is>
       </c>
       <c r="F2089" s="11" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2090">
       <c r="A2090" s="11" t="inlineStr">
         <is>
-          <t>14960213</t>
+          <t>15299455</t>
         </is>
       </c>
       <c r="B2090" s="11" t="inlineStr">
         <is>
-          <t>Kopparberg Poire 0% (4 x 500 ml)</t>
+          <t>Twisted Tea Originale Bouteille 6 x 341 ml</t>
         </is>
       </c>
       <c r="C2090" s="11" t="inlineStr">
         <is>
-          <t>Dépôt Québec</t>
+          <t>Saint-Félicien</t>
         </is>
       </c>
       <c r="D2090" s="11" t="inlineStr">
         <is>
-          <t>SAQ Dépôt</t>
+          <t>SAQ</t>
         </is>
       </c>
       <c r="E2090" s="11" t="inlineStr">
         <is>
-          <t>Québec</t>
+          <t>Saint-Félicien</t>
         </is>
       </c>
       <c r="F2090" s="11" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="2091">
@@ -68723,7 +68723,7 @@
       </c>
       <c r="C2091" s="11" t="inlineStr">
         <is>
-          <t>Saint-Félicien</t>
+          <t>Pointe-à-la-Croix</t>
         </is>
       </c>
       <c r="D2091" s="11" t="inlineStr">
@@ -68733,7 +68733,7 @@
       </c>
       <c r="E2091" s="11" t="inlineStr">
         <is>
-          <t>Saint-Félicien</t>
+          <t>Pointe-à-la-Croix</t>
         </is>
       </c>
       <c r="F2091" s="11" t="n">
@@ -68743,31 +68743,31 @@
     <row r="2092">
       <c r="A2092" s="11" t="inlineStr">
         <is>
-          <t>15299455</t>
+          <t>15078249</t>
         </is>
       </c>
       <c r="B2092" s="11" t="inlineStr">
         <is>
-          <t>Twisted Tea Originale Bouteille 6 x 341 ml</t>
+          <t>Kopparberg Mangue sans alcool (4 x 500 ml)</t>
         </is>
       </c>
       <c r="C2092" s="11" t="inlineStr">
         <is>
-          <t>Pointe-à-la-Croix</t>
+          <t>Saint-Lambert - Boul. Sir-Wilfrid-Laurier</t>
         </is>
       </c>
       <c r="D2092" s="11" t="inlineStr">
         <is>
-          <t>SAQ</t>
+          <t>SAQ Sélection</t>
         </is>
       </c>
       <c r="E2092" s="11" t="inlineStr">
         <is>
-          <t>Pointe-à-la-Croix</t>
+          <t>Saint-Lambert</t>
         </is>
       </c>
       <c r="F2092" s="11" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="2093">
@@ -68783,7 +68783,7 @@
       </c>
       <c r="C2093" s="11" t="inlineStr">
         <is>
-          <t>Saint-Lambert - Boul. Sir-Wilfrid-Laurier</t>
+          <t>Dorval</t>
         </is>
       </c>
       <c r="D2093" s="11" t="inlineStr">
@@ -68793,11 +68793,11 @@
       </c>
       <c r="E2093" s="11" t="inlineStr">
         <is>
-          <t>Saint-Lambert</t>
+          <t>Dorval</t>
         </is>
       </c>
       <c r="F2093" s="11" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="2094">
@@ -68813,7 +68813,7 @@
       </c>
       <c r="C2094" s="11" t="inlineStr">
         <is>
-          <t>Dorval</t>
+          <t>Châteauguay - Boul. D'Anjou</t>
         </is>
       </c>
       <c r="D2094" s="11" t="inlineStr">
@@ -68823,11 +68823,11 @@
       </c>
       <c r="E2094" s="11" t="inlineStr">
         <is>
-          <t>Dorval</t>
+          <t>Châteauguay</t>
         </is>
       </c>
       <c r="F2094" s="11" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="2095">
@@ -68843,21 +68843,21 @@
       </c>
       <c r="C2095" s="11" t="inlineStr">
         <is>
-          <t>Châteauguay - Boul. D'Anjou</t>
+          <t>Lorraine</t>
         </is>
       </c>
       <c r="D2095" s="11" t="inlineStr">
         <is>
-          <t>SAQ Sélection</t>
+          <t>SAQ</t>
         </is>
       </c>
       <c r="E2095" s="11" t="inlineStr">
         <is>
-          <t>Châteauguay</t>
+          <t>Lorraine</t>
         </is>
       </c>
       <c r="F2095" s="11" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="2096">
@@ -68873,21 +68873,21 @@
       </c>
       <c r="C2096" s="11" t="inlineStr">
         <is>
-          <t>Lorraine</t>
+          <t>Blainville</t>
         </is>
       </c>
       <c r="D2096" s="11" t="inlineStr">
         <is>
-          <t>SAQ</t>
+          <t>SAQ Sélection</t>
         </is>
       </c>
       <c r="E2096" s="11" t="inlineStr">
         <is>
-          <t>Lorraine</t>
+          <t>Blainville</t>
         </is>
       </c>
       <c r="F2096" s="11" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="2097">
@@ -68903,7 +68903,7 @@
       </c>
       <c r="C2097" s="11" t="inlineStr">
         <is>
-          <t>Blainville</t>
+          <t>L'Île-Perrot</t>
         </is>
       </c>
       <c r="D2097" s="11" t="inlineStr">
@@ -68913,11 +68913,11 @@
       </c>
       <c r="E2097" s="11" t="inlineStr">
         <is>
-          <t>Blainville</t>
+          <t>L'Île-Perrot</t>
         </is>
       </c>
       <c r="F2097" s="11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="2098">
@@ -68933,7 +68933,7 @@
       </c>
       <c r="C2098" s="11" t="inlineStr">
         <is>
-          <t>L'Île-Perrot</t>
+          <t>Sainte-Agathe-des-Monts</t>
         </is>
       </c>
       <c r="D2098" s="11" t="inlineStr">
@@ -68943,7 +68943,7 @@
       </c>
       <c r="E2098" s="11" t="inlineStr">
         <is>
-          <t>L'Île-Perrot</t>
+          <t>Sainte-Agathe-des-Monts</t>
         </is>
       </c>
       <c r="F2098" s="11" t="n">
@@ -68963,7 +68963,7 @@
       </c>
       <c r="C2099" s="11" t="inlineStr">
         <is>
-          <t>Sainte-Agathe-des-Monts</t>
+          <t>Victoriaville - Boul. Jutras</t>
         </is>
       </c>
       <c r="D2099" s="11" t="inlineStr">
@@ -68973,11 +68973,11 @@
       </c>
       <c r="E2099" s="11" t="inlineStr">
         <is>
-          <t>Sainte-Agathe-des-Monts</t>
+          <t>Victoriaville</t>
         </is>
       </c>
       <c r="F2099" s="11" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
     </row>
     <row r="2100">
@@ -68993,7 +68993,7 @@
       </c>
       <c r="C2100" s="11" t="inlineStr">
         <is>
-          <t>Victoriaville - Boul. Jutras</t>
+          <t>Place Naviles</t>
         </is>
       </c>
       <c r="D2100" s="11" t="inlineStr">
@@ -69003,11 +69003,11 @@
       </c>
       <c r="E2100" s="11" t="inlineStr">
         <is>
-          <t>Victoriaville</t>
+          <t>Québec</t>
         </is>
       </c>
       <c r="F2100" s="11" t="n">
-        <v>11</v>
+        <v>101</v>
       </c>
     </row>
     <row r="2101">
@@ -69023,67 +69023,67 @@
       </c>
       <c r="C2101" s="11" t="inlineStr">
         <is>
-          <t>Place Naviles</t>
+          <t>Saint-Jean-Chrysostome</t>
         </is>
       </c>
       <c r="D2101" s="11" t="inlineStr">
         <is>
-          <t>SAQ Sélection</t>
+          <t>SAQ</t>
         </is>
       </c>
       <c r="E2101" s="11" t="inlineStr">
         <is>
-          <t>Québec</t>
+          <t>Lévis</t>
         </is>
       </c>
       <c r="F2101" s="11" t="n">
-        <v>101</v>
+        <v>1</v>
       </c>
     </row>
     <row r="2102">
       <c r="A2102" s="11" t="inlineStr">
         <is>
-          <t>15078249</t>
+          <t>15162184</t>
         </is>
       </c>
       <c r="B2102" s="11" t="inlineStr">
         <is>
-          <t>Kopparberg Mangue sans alcool (4 x 500 ml)</t>
+          <t>Palm Bay Peche Citron Zero Sucre (4 x 355 ml)</t>
         </is>
       </c>
       <c r="C2102" s="11" t="inlineStr">
         <is>
-          <t>Saint-Jean-Chrysostome</t>
+          <t>Laval - Auteuil</t>
         </is>
       </c>
       <c r="D2102" s="11" t="inlineStr">
         <is>
-          <t>SAQ</t>
+          <t>SAQ Sélection</t>
         </is>
       </c>
       <c r="E2102" s="11" t="inlineStr">
         <is>
-          <t>Lévis</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F2102" s="11" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="2103">
       <c r="A2103" s="11" t="inlineStr">
         <is>
-          <t>15162184</t>
+          <t>15148219</t>
         </is>
       </c>
       <c r="B2103" s="11" t="inlineStr">
         <is>
-          <t>Palm Bay Peche Citron Zero Sucre (4 x 355 ml)</t>
+          <t>Palm Bay Fraise Ananas Zero Sucre (4 x 355 ml)</t>
         </is>
       </c>
       <c r="C2103" s="11" t="inlineStr">
         <is>
-          <t>Laval - Auteuil</t>
+          <t>Carrefour de la Pointe</t>
         </is>
       </c>
       <c r="D2103" s="11" t="inlineStr">
@@ -69093,130 +69093,70 @@
       </c>
       <c r="E2103" s="11" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Montréal</t>
         </is>
       </c>
       <c r="F2103" s="11" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
     </row>
     <row r="2104">
       <c r="A2104" s="11" t="inlineStr">
         <is>
-          <t>15148534</t>
+          <t>14959802</t>
         </is>
       </c>
       <c r="B2104" s="11" t="inlineStr">
         <is>
-          <t>Palm Bay Framboise Bleue Citron Zero Sucre (4 x 355 ml)</t>
+          <t>Kopparberg Mangue et Framb 0% (4 x 500 ml)</t>
         </is>
       </c>
       <c r="C2104" s="11" t="inlineStr">
         <is>
-          <t>Saint-Félicien</t>
+          <t>De Maisonneuve - City Councillors</t>
         </is>
       </c>
       <c r="D2104" s="11" t="inlineStr">
         <is>
-          <t>SAQ</t>
+          <t>SAQ Sélection</t>
         </is>
       </c>
       <c r="E2104" s="11" t="inlineStr">
         <is>
-          <t>Saint-Félicien</t>
+          <t>Montréal</t>
         </is>
       </c>
       <c r="F2104" s="11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2105">
       <c r="A2105" s="11" t="inlineStr">
         <is>
-          <t>15148219</t>
+          <t>14959802</t>
         </is>
       </c>
       <c r="B2105" s="11" t="inlineStr">
         <is>
-          <t>Palm Bay Fraise Ananas Zero Sucre (4 x 355 ml)</t>
+          <t>Kopparberg Mangue et Framb 0% (4 x 500 ml)</t>
         </is>
       </c>
       <c r="C2105" s="11" t="inlineStr">
         <is>
-          <t>Carrefour de la Pointe</t>
+          <t>Sainte-Perpétue</t>
         </is>
       </c>
       <c r="D2105" s="11" t="inlineStr">
         <is>
-          <t>SAQ Sélection</t>
+          <t>SAQ</t>
         </is>
       </c>
       <c r="E2105" s="11" t="inlineStr">
         <is>
-          <t>Montréal</t>
+          <t>Ste-Perpétue de l'Islet</t>
         </is>
       </c>
       <c r="F2105" s="11" t="n">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="2106">
-      <c r="A2106" s="11" t="inlineStr">
-        <is>
-          <t>14959802</t>
-        </is>
-      </c>
-      <c r="B2106" s="11" t="inlineStr">
-        <is>
-          <t>Kopparberg Mangue et Framb 0% (4 x 500 ml)</t>
-        </is>
-      </c>
-      <c r="C2106" s="11" t="inlineStr">
-        <is>
-          <t>De Maisonneuve - City Councillors</t>
-        </is>
-      </c>
-      <c r="D2106" s="11" t="inlineStr">
-        <is>
-          <t>SAQ Sélection</t>
-        </is>
-      </c>
-      <c r="E2106" s="11" t="inlineStr">
-        <is>
-          <t>Montréal</t>
-        </is>
-      </c>
-      <c r="F2106" s="11" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="2107">
-      <c r="A2107" s="11" t="inlineStr">
-        <is>
-          <t>14959802</t>
-        </is>
-      </c>
-      <c r="B2107" s="11" t="inlineStr">
-        <is>
-          <t>Kopparberg Mangue et Framb 0% (4 x 500 ml)</t>
-        </is>
-      </c>
-      <c r="C2107" s="11" t="inlineStr">
-        <is>
-          <t>Sainte-Perpétue</t>
-        </is>
-      </c>
-      <c r="D2107" s="11" t="inlineStr">
-        <is>
-          <t>SAQ</t>
-        </is>
-      </c>
-      <c r="E2107" s="11" t="inlineStr">
-        <is>
-          <t>Ste-Perpétue de l'Islet</t>
-        </is>
-      </c>
-      <c r="F2107" s="11" t="n">
         <v>3</v>
       </c>
     </row>
